--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Theo dõi công việc'!$A$4:$O$44</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -1965,13 +1965,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C5-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M5" s="22" t="s">
-        <v>62</v>
+      <c r="M5" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>Compose/Dockerfile build OK; MinIO+Postgres đã chạy. Chưa kiểm chứng webserver/scheduler end-to-end (21/10)</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="n">
@@ -2011,13 +2017,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C6-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M6" s="22" t="s">
-        <v>62</v>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t>Đã có 3 bucket và key đúng quy ước. Còn thiếu: Bronze chưa giữ nguyên payload gốc (_pipeline_metadata)</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="n">
@@ -2059,13 +2071,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C7-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M7" s="22" t="s">
-        <v>62</v>
+      <c r="M7" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="O7" s="24" t="inlineStr">
+        <is>
+          <t>DDL + sơ đồ star schema (outputs/dfd-weather-20261013). Còn mở: cơ sở lịch, nhiều trạm, prediction</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="n">
@@ -2197,13 +2215,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C10-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M10" s="22" t="s">
-        <v>62</v>
+      <c r="M10" s="22" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
       </c>
       <c r="N10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="24"/>
+        <v>100</v>
+      </c>
+      <c r="O10" s="24" t="inlineStr">
+        <is>
+          <t>Hoàn thành 21/10: data-contract.md v0.2 (cột/đơn vị/UTC/pressure_type/xử lý trùng/chọn trạm/báo cáo độ phủ). Nhóm xác nhận (qua N1/N2). Còn để mở có ghi rõ: ngưỡng độ phủ tối thiểu</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="n">
@@ -2243,13 +2267,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C11-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M11" s="22" t="s">
-        <v>62</v>
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
       </c>
       <c r="N11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="24"/>
+        <v>100</v>
+      </c>
+      <c r="O11" s="24" t="inlineStr">
+        <is>
+          <t>Hoàn thành 21/10: rain-label.md v0.2: ngưỡng 1 mm (Yes 50,5% trên 2016–2025), nguồn Open-Meteo, cửa sổ (t,t+24h] đã kiểm chứng, thiếu giờ thì bỏ nhãn. Nhóm xác nhận (qua N1/N2). Còn để mở có ghi rõ: fallback ERA5</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="n">
@@ -2289,13 +2319,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C12-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M12" s="22" t="s">
-        <v>62</v>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>21/10: chạy lại trên máy N1/N2: 80/80 file Bronze (8 điểm × 2016–2025), 0 lỗi, 326 s. Còn lệch: Bronze chưa giữ nguyên payload gốc, thiếu manifest</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="n">
@@ -2335,13 +2371,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C13-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M13" s="22" t="s">
-        <v>62</v>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="24"/>
+        <v>70</v>
+      </c>
+      <c r="O13" s="24" t="inlineStr">
+        <is>
+          <t>21/10: registry trạm đã sửa; Meteostat chỉ giữ giá trị quan trắc thật (lọc theo &lt;var&gt;_source). Còn HAN/48820 2016–2025: 87.485 dòng, không có mưa đo thật (mưa đều là mô hình). HPH chỉ có dữ liệu mô hình nên bị loại. NOAA chưa làm, cần nếu muốn có mưa trạm | 21/10 NOAA ISD (kiểm tra 2024): không có mưa theo giờ; có mưa 24h (12 UTC) cho HPH 488260, TNG 488310, LCA 488030, HAN≈Hà Đông 488250, NBI≈Nam Định 488230; cần quyết định bảng mưa ngày</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="n">
@@ -2381,13 +2423,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C14-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M14" s="22" t="s">
-        <v>62</v>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="n">
@@ -2427,13 +2475,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C15-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M15" s="22" t="s">
-        <v>62</v>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="24"/>
+        <v>60</v>
+      </c>
+      <c r="O15" s="24" t="inlineStr">
+        <is>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD), dim_station seed lại 11 trạm. Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803. Ánh xạ tỉnh cũ-mới chưa làm</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="n">
@@ -2473,13 +2527,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C16-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M16" s="22" t="s">
-        <v>62</v>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>dim_date 4.018 ngày, seed chạy lại ổn; cơ sở lịch UTC+7 cần cả nhóm xác nhận</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="n">
@@ -2519,13 +2579,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C17-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M17" s="22" t="s">
-        <v>62</v>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="O17" s="24" t="inlineStr">
+        <is>
+          <t>DDL chạy được trên Postgres; chưa có migration cho DB đã tồn tại</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="n">
@@ -2657,13 +2723,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C20-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M20" s="22" t="s">
-        <v>62</v>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="O20" s="24" t="inlineStr">
+        <is>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2: 832.436 dòng, 120 tháng, 0 lỗi, 233 s. Chưa tách bảng pivot cho ML</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="n">
@@ -2751,13 +2823,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C22-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M22" s="22" t="s">
-        <v>62</v>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N22" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O22" s="24" t="inlineStr">
+        <is>
+          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; chạy lại 2024 không đổi số liệu. Lần nạp cuối chậm (3.493 s, máy có thể đã ngủ). Bản 994.145 dòng trên máy bacnx đã lỗi thời</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="n">
@@ -2935,13 +3013,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C26-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M26" s="22" t="s">
-        <v>62</v>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N26" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="24"/>
+        <v>40</v>
+      </c>
+      <c r="O26" s="24" t="inlineStr">
+        <is>
+          <t>21/10: scripts/rain_labels.py (cửa sổ (t,t+24h], ngưỡng 1 mm, thiếu giờ thì không nhãn, loại mẫu ở ranh giới tập) + 10 unit test. Chạy thử trên Open-Meteo 2016–2025: 700.800 nhãn dùng được, 576 bị loại ở ranh giới. Chưa xuất bảng nhãn từ Silver/Gold</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2875,13 +2875,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C23-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M23" s="22" t="s">
-        <v>62</v>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N23" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O23" s="24" t="inlineStr">
+        <is>
+          <t>21/10: sql/02_olap_views.sql (6 view giờ/ngày/tháng/năm/độ phủ), ngày mưa ≥1 mm, ngày nóng ≥35 °C; đối soát giờ→ngày→tháng→năm khớp 0 chênh trên 788.861 dòng; 3 test tích hợp. Chưa dùng trong Power BI</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2377,11 +2377,11 @@
         </is>
       </c>
       <c r="N13" s="23" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>21/10: registry trạm đã sửa; Meteostat chỉ giữ giá trị quan trắc thật (lọc theo &lt;var&gt;_source). Còn HAN/48820 2016–2025: 87.485 dòng, không có mưa đo thật (mưa đều là mô hình). HPH chỉ có dữ liệu mô hình nên bị loại. NOAA chưa làm, cần nếu muốn có mưa trạm | 21/10 NOAA ISD (kiểm tra 2024): không có mưa theo giờ; có mưa 24h (12 UTC) cho HPH 488260, TNG 488310, LCA 488030, HAN≈Hà Đông 488250, NBI≈Nam Định 488230; cần quyết định bảng mưa ngày</t>
+          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. Chờ nhóm duyệt quy tắc cực trị 300 mm</t>
         </is>
       </c>
     </row>
@@ -2927,13 +2927,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C24-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M24" s="22" t="s">
-        <v>62</v>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N24" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="24"/>
+        <v>30</v>
+      </c>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>21/10: có hướng dẫn dựng (docs/powerbi-dashboard-v1.md): mô hình, DAX, 5 trang, bảng số đối chiếu. Chưa có file .pbix (cần máy Windows), chưa kiểm tra trong Power BI</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3031,11 +3031,11 @@
         </is>
       </c>
       <c r="N26" s="23" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>21/10: scripts/rain_labels.py (cửa sổ (t,t+24h], ngưỡng 1 mm, thiếu giờ thì không nhãn, loại mẫu ở ranh giới tập) + 10 unit test. Chạy thử trên Open-Meteo 2016–2025: 700.800 nhãn dùng được, 576 bị loại ở ranh giới. Chưa xuất bảng nhãn từ Silver/Gold</t>
+          <t>21/10: gold/ml_labels/rain_next24h_labels_v1.parquet + manifest: 700.800 nhãn dùng được (train 560.832 / val 70.080 / test 69.888; Yes 50,9% / 49,4% / 49,0%), 576 mẫu loại ở ranh giới. Test t/t+1/t+24/t+25, thiếu giờ, ranh giới. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2979,13 +2979,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C25-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M25" s="22" t="s">
-        <v>62</v>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O25" s="24" t="inlineStr">
+        <is>
+          <t>21/10: notebooks/eda_rain_next24h.ipynb (chạy trên dữ liệu thật, chỉ dùng tập train để chọn biến): mùa vụ mạnh (T8 78%, T12 26%), giờ trong ngày gần như không ảnh hưởng, biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm, áp suất. Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3083,13 +3083,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C27-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M27" s="22" t="s">
-        <v>62</v>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N27" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O27" s="24" t="inlineStr">
+        <is>
+          <t>21/10: gold/ml_features/cart_rain_{train_2016_2023,val_2024,test_2025}_v1.parquet + manifest: 22 đặc trưng chỉ từ Open-Meteo (giá trị tại t, trễ 3/6h, mưa 3/6/12/24h trước, TB 6h, biến thiên áp suất 3h/24h, giờ/tháng địa phương). 700.800 dòng = đúng số nhãn dùng được; thiếu giá trị chỉ ở 24 giờ đầu 2016 (192 dòng). Test chống rò rỉ, thiếu giờ, không lẫn vị trí. Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3321,13 +3321,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C32-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M32" s="22" t="s">
-        <v>62</v>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N32" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình fit trên train 2016-2023, chọn trên validation 2024 theo F1: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng xác suất 0,40. Validation: Precision 0,752 / Recall 0,822 / F1 0,786 (mốc dự báo theo hiện trạng F1 0,753). Chưa đọc tập test. Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3373,13 +3373,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C33-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M33" s="22" t="s">
-        <v>62</v>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N33" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>21/10: đánh giá 1 lần trên test 2025 với model + ngưỡng 0,40 đã chốt từ validation (không chỉnh ngưỡng bằng test). 69.888/69.888 mẫu. TP 27.254 / FP 8.782 / TN 26.840 / FN 7.012; Accuracy 0,774, Precision 0,756, Recall 0,795, F1 0,775 (dự báo theo hiện trạng F1 0,726). Mùa mưa F1 0,835, mùa khô 0,621. gold/ml_models/cart_rain_next24h_v1/test_evaluation.json. Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3425,13 +3425,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C34-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M34" s="22" t="s">
-        <v>62</v>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N34" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>21/10: notebooks/cart_tree_rules.ipynb (kiểm tra SHA-256 đúng model đã đánh giá ở ID 29): hình 3 tầng đầu cây, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025 (TP/FP/FN cực đoan/FN điển hình), hồ sơ ca bỏ sót trên validation 2024: 64% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,6%). Đã sửa lời diễn giải «mưa không báo trước» (suy từ 1 ví dụ). Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3479,13 +3479,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C35-1)*7+4</f>
         <v>46360</v>
       </c>
-      <c r="M35" s="22" t="s">
-        <v>62</v>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N35" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O35" s="24" t="inlineStr">
+        <is>
+          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu phát hiện lỗi nhãn ID 22 (tổng đúng 1,0 mm bị gán Không mưa, 0,73% nhãn); đang sửa. Do N1/N2 làm thay N3</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2989,7 +2989,7 @@
       </c>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>21/10: notebooks/eda_rain_next24h.ipynb (chạy trên dữ liệu thật, chỉ dùng tập train để chọn biến): mùa vụ mạnh (T8 78%, T12 26%), giờ trong ngày gần như không ảnh hưởng, biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm, áp suất. Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
+          <t>22/10 (chạy lại với nhãn đã sửa): notebooks/eda_rain_next24h.ipynb, chỉ dùng train để chọn biến: mùa vụ mạnh (T8 78,5%, T12 26,3%), giờ trong ngày gần như không ảnh hưởng (51,3-52,0%), biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm. Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_labels/rain_next24h_labels_v1.parquet + manifest: 700.800 nhãn dùng được (train 560.832 / val 70.080 / test 69.888; Yes 50,9% / 49,4% / 49,0%), 576 mẫu loại ở ranh giới. Test t/t+1/t+24/t+25, thiếu giờ, ranh giới. Do N1/N2 làm thay N3</t>
+          <t>22/10: nhãn v2 (rain_next24h_v0.2.1) gold/ml_labels/rain_next24h_labels_v2.parquet: 700.800 nhãn dùng được, Yes 51,6% / 50,1% / 49,7% (train/val/test), 576 loại ở ranh giới. Đã sửa lỗi cộng số thực: bản v1 gán Không mưa cho 5.147 cửa sổ đúng 1,0 mm (0,73%); phát hiện nhờ đối chiếu DW ở ID 31. Có test hồi quy. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="O27" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_features/cart_rain_{train_2016_2023,val_2024,test_2025}_v1.parquet + manifest: 22 đặc trưng chỉ từ Open-Meteo (giá trị tại t, trễ 3/6h, mưa 3/6/12/24h trước, TB 6h, biến thiên áp suất 3h/24h, giờ/tháng địa phương). 700.800 dòng = đúng số nhãn dùng được; thiếu giá trị chỉ ở 24 giờ đầu 2016 (192 dòng). Test chống rò rỉ, thiếu giờ, không lẫn vị trí. Do N1/N2 làm thay N3</t>
+          <t>22/10: đặc trưng v2 gold/ml_features/cart_rain_{train_2016_2023,val_2024,test_2025}_v2.parquet + manifest (nhãn v0.2.1, tổng mưa làm tròn); v1 giữ cho model v1. 22 đặc trưng chỉ từ Open-Meteo, 700.800 dòng; thiếu chỉ ở 24 giờ đầu 2016. Test chống rò rỉ, thiếu giờ, không lẫn vị trí. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình fit trên train 2016-2023, chọn trên validation 2024 theo F1: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng xác suất 0,40. Validation: Precision 0,752 / Recall 0,822 / F1 0,786 (mốc dự báo theo hiện trạng F1 0,753). Chưa đọc tập test. Do N1/N2 làm thay N3</t>
+          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>21/10: đánh giá 1 lần trên test 2025 với model + ngưỡng 0,40 đã chốt từ validation (không chỉnh ngưỡng bằng test). 69.888/69.888 mẫu. TP 27.254 / FP 8.782 / TN 26.840 / FN 7.012; Accuracy 0,774, Precision 0,756, Recall 0,795, F1 0,775 (dự báo theo hiện trạng F1 0,726). Mùa mưa F1 0,835, mùa khô 0,621. gold/ml_models/cart_rain_next24h_v1/test_evaluation.json. Do N1/N2 làm thay N3</t>
+          <t>22/10: đánh giá 1 lần trên test 2025, model + ngưỡng 0,40 chốt từ validation. Chấm lại với nhãn đã sửa (dự đoán giữ nguyên): TP 27.467 / FP 8.569 / TN 26.617 / FN 7.235; Accuracy 0,774, Precision 0,762, Recall 0,792, F1 0,777 (dự báo theo hiện trạng F1 0,729). Mùa mưa F1 0,836, mùa khô 0,624. Khớp hoàn toàn với view DW. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>21/10: notebooks/cart_tree_rules.ipynb (kiểm tra SHA-256 đúng model đã đánh giá ở ID 29): hình 3 tầng đầu cây, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025 (TP/FP/FN cực đoan/FN điển hình), hồ sơ ca bỏ sót trên validation 2024: 64% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,6%). Đã sửa lời diễn giải «mưa không báo trước» (suy từ 1 ví dụ). Do N1/N2 làm thay N3</t>
+          <t>22/10: notebooks/cart_tree_rules.ipynb (SHA-256 đúng model ID 29): hình 3 tầng đầu, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025, hồ sơ ca bỏ sót trên validation (nhãn đã sửa): 65% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,5%). Đã sửa lời diễn giải «mưa không báo trước». Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu phát hiện lỗi nhãn ID 22 (tổng đúng 1,0 mm bị gán Không mưa, 0,73% nhãn); đang sửa. Do N1/N2 làm thay N3</t>
+          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu đã phát hiện lỗi nhãn ID 22 (đã sửa); sau khi sửa, ma trận nhầm lẫn DW = kết quả chấm lại. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t>DDL + sơ đồ star schema (outputs/dfd-weather-20261013). Còn mở: cơ sở lịch, nhiều trạm, prediction</t>
+          <t>22/10: DDL + sơ đồ star schema (outputs/dfd-weather-20261013, chỉ có trên máy cục bộ vì outputs/ không đưa lên Git). Đã chốt: cơ sở lịch UTC+7; prediction (sql/04, sql/05). Còn mở: nhiều trạm/nguồn trên cùng điểm</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,11 @@
       <c r="N8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="24"/>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. 21/10 N1/N2 đề xuất đổi phạm vi sang ranh giới trước sáp nhập (63 tỉnh) vì giai đoạn nghiên cứu gần như toàn bộ trước 1/7/2025; chờ nhóm xác nhận. Nguồn ứng viên và tiêu chí: task-specs §7; kế hoạch: business-requirements §5a</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="n">
@@ -2175,7 +2179,11 @@
       <c r="N9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="24"/>
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t>22/10: chưa bắt đầu, trễ hạn tuần 1; thiếu ERA5 nên chưa đạt mục tiêu đa định dạng (NetCDF). Đề xuất phạm vi và thứ tự (ID 4 → ID 5 → ID 14/15) ở business-requirements §5a; chỉ tải khi N3 xác nhận phạm vi</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="n">
@@ -2277,7 +2285,7 @@
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>Hoàn thành 21/10: rain-label.md v0.2: ngưỡng 1 mm (Yes 50,5% trên 2016–2025), nguồn Open-Meteo, cửa sổ (t,t+24h] đã kiểm chứng, thiếu giờ thì bỏ nhãn. Nhóm xác nhận (qua N1/N2). Còn để mở có ghi rõ: fallback ERA5</t>
+          <t>Hoàn thành 21/10: rain-label.md v0.2: ngưỡng 1 mm, nguồn Open-Meteo, cửa sổ (t,t+24h] đã kiểm chứng, thiếu giờ thì bỏ nhãn. Tỷ lệ Yes 50,5% đo bằng bản v0.2; bản v0.2.1 (sửa lỗi cộng số thực 22/10): train 51,6% / val 50,1% / test 49,7%. Nhóm xác nhận qua N1/N2; N3 chưa duyệt. Còn mở có ghi rõ: fallback ERA5/trạm, ngưỡng độ phủ tối thiểu</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2337,7 @@
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>21/10: chạy lại trên máy N1/N2: 80/80 file Bronze (8 điểm × 2016–2025), 0 lỗi, 326 s. Còn lệch: Bronze chưa giữ nguyên payload gốc, thiếu manifest</t>
+          <t>21/10: chạy lại trên máy N1/N2: 80/80 file Bronze (8 điểm × 2016–2025), 326 s; «0 lỗi» dựa trên số object vì script khi đó vẫn thoát mã 0 khi có file lỗi. 22/10: đã sửa: file lỗi → thoát mã 1 sau khi thử hết các file còn lại, chỉ thử lại lỗi 429/5xx/mạng; Silver coi file Bronze thiếu là lỗi. Còn lệch: Bronze chưa giữ nguyên payload gốc, thiếu manifest</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2389,7 @@
       </c>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. Chờ nhóm duyệt quy tắc cực trị 300 mm</t>
+          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. 22/10: trạm Meteostat 48820 thực chất là sân bay Nội Bài (cách điểm HAN 22 km), đã ghi lại; quy tắc cực trị so sánh theo độ phân giải 0,1 mm. Bronze Meteostat lưu CSV đã giải nén, chưa có manifest/SHA. Chờ nhóm duyệt quy tắc cực trị 300 mm</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2493,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD), dim_station seed lại 11 trạm. Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803. Ánh xạ tỉnh cũ-mới chưa làm</t>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh cũ-mới: không làm theo đề xuất ranh giới trước sáp nhập, chờ nhóm xác nhận</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2545,7 @@
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>dim_date 4.018 ngày, seed chạy lại ổn; cơ sở lịch UTC+7 cần cả nhóm xác nhận</t>
+          <t>dim_date 4.018 ngày, seed chạy lại ổn. Cơ sở lịch UTC+7 đã chốt 21/10 (data-contract, warehouse-schema; nhóm xác nhận qua N1/N2)</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2597,7 @@
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>DDL chạy được trên Postgres; chưa có migration cho DB đã tồn tại</t>
+          <t>DDL chạy được trên Postgres; migration cho DB đã tồn tại: sql/02–05, chạy lại an toàn. 22/10: test tích hợp chạy đúng thứ tự khởi tạo thật (init + 02→05); sửa chú thích day_of_week (ISO) và period_of_day</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2741,7 @@
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2: 832.436 dòng, 120 tháng, 0 lỗi, 233 s. Chưa tách bảng pivot cho ML</t>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: station_key trong Gold lưu dạng số nguyên (đã áp dụng cho 2024; các năm khác khi nạp lại). Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2841,7 @@
       </c>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; chạy lại 2024 không đổi số liệu. Lần nạp cuối chậm (3.493 s, máy có thể đã ngủ). Bản 994.145 dòng trên máy bacnx đã lỗi thời</t>
+          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; lần nạp cuối 292 s (bản trước ghi 3.493 s là sai). 22/10: phạm vi xóa khi nạp lại tính theo phạm vi yêu cầu (nguồn biến mất bị xóa; thiếu file Silver Open-Meteo của một vị trí thì tháng đó báo lỗi); thêm pressure_type (sql/05). Chạy lại 2024 trên trạng thái hiện tại: 79.039 dòng, không đổi. Bản 994.145 dòng trên máy bacnx đã lỗi thời</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2945,7 @@
       </c>
       <c r="O24" s="24" t="inlineStr">
         <is>
-          <t>21/10: có hướng dẫn dựng (docs/powerbi-dashboard-v1.md): mô hình, DAX, 5 trang, bảng số đối chiếu. Chưa có file .pbix (cần máy Windows), chưa kiểm tra trong Power BI</t>
+          <t>21/10: có hướng dẫn dựng (docs/powerbi-dashboard-v1.md): mô hình, DAX, 5 trang, bảng số đối chiếu. 22/10: sửa DAX đếm ngày mưa/nóng (trả 0 thay vì trống; trước đó trung bình theo vị trí bị lệch, vd tháng 3/2024 ra 1,33 thay vì 0,50). Chưa có file .pbix (cần máy Windows), chưa kiểm tra trong Power BI</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2997,7 @@
       </c>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>22/10 (chạy lại với nhãn đã sửa): notebooks/eda_rain_next24h.ipynb, chỉ dùng train để chọn biến: mùa vụ mạnh (T8 78,5%, T12 26,3%), giờ trong ngày gần như không ảnh hưởng (51,3-52,0%), biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm. Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
+          <t>22/10: notebooks/eda_rain_next24h.ipynb (nhãn đã sửa), chỉ dùng train để chọn biến: mùa vụ mạnh theo tháng giờ Việt Nam (T8 78,6%, T12 26,5%; bản trước dùng tháng UTC), giờ trong ngày gần như không ảnh hưởng (51,3-52,0%), biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm. Thêm bảng tương quan Spearman: cặp mạnh độ ẩm–chênh điểm sương (-1,00), nhiệt độ–điểm sương (0,87), điểm sương–áp suất (-0,80). Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3339,7 @@
       </c>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. Do N1/N2 làm thay N3</t>
+          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. 22/10: chặn ghi đè model (model đã chấm test thì không cho ghi đè). Chọn cấu hình và ngưỡng theo F1, chưa có quy tắc ưu tiên Recall (đề xuất chờ duyệt). Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3391,7 @@
       </c>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>22/10: đánh giá 1 lần trên test 2025, model + ngưỡng 0,40 chốt từ validation. Chấm lại với nhãn đã sửa (dự đoán giữ nguyên): TP 27.467 / FP 8.569 / TN 26.617 / FN 7.235; Accuracy 0,774, Precision 0,762, Recall 0,792, F1 0,777 (dự báo theo hiện trạng F1 0,729). Mùa mưa F1 0,836, mùa khô 0,624. Khớp hoàn toàn với view DW. Do N1/N2 làm thay N3</t>
+          <t>22/10: đánh giá 1 lần trên test 2025, model + ngưỡng 0,40 chốt từ validation. Chấm lại với nhãn đã sửa (dự đoán giữ nguyên, kiểm SHA-256 model): TP 27.467 / FP 8.569 / TN 26.617 / FN 7.235; Accuracy 0,774, Precision 0,762, Recall 0,792, F1 0,777 (dự báo theo hiện trạng F1 0,729). Mùa mưa F1 0,836, mùa khô 0,624. Khớp hoàn toàn với view DW. test_predictions.parquet giữ nhãn cũ v0.2: phân tích lấy nhãn từ đặc trưng v2. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3443,7 @@
       </c>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>22/10: notebooks/cart_tree_rules.ipynb (SHA-256 đúng model ID 29): hình 3 tầng đầu, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025, hồ sơ ca bỏ sót trên validation (nhãn đã sửa): 65% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,5%). Đã sửa lời diễn giải «mưa không báo trước». Do N1/N2 làm thay N3</t>
+          <t>22/10: notebooks/cart_tree_rules.ipynb (SHA-256 đúng model ID 29): hình 3 tầng đầu, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025, hồ sơ ca bỏ sót trên validation (nhãn đã sửa): 65% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,5%). Đã sửa lời diễn giải «mưa không báo trước». Ý tưởng thêm hướng gió đến từ một ví dụ test 2025: phải chứng minh bằng EDA trên train trước. Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu đã phát hiện lỗi nhãn ID 22 (đã sửa); sau khi sửa, ma trận nhầm lẫn DW = kết quả chấm lại. Do N1/N2 làm thay N3</t>
+          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu đã phát hiện lỗi nhãn ID 22 (đã sửa); ma trận nhầm lẫn DW = kết quả chấm lại. sql/05: dim_model ghi rõ nhãn của từng chỉ số (chọn trên v0.2, F1 val 0,786; test trên v0.2.1, F1 val trên nhãn này 0,789). Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4137,11 @@
       <c r="E4" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="24"/>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>22/10: ID 5 chưa bắt đầu; đề xuất phạm vi và thứ tự ở docs/business-requirements.md §5a</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
@@ -4183,7 +4195,11 @@
       <c r="E7" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F7" s="24"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>22/10: gán trạm bằng khoảng cách haversine (scripts/station_config.py). HAN: Meteostat là sân bay Nội Bài (22 km); mưa ngày lấy Hà Đông (11,3 km). PTO, TUQ, HBI không có trạm</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
@@ -4219,7 +4235,11 @@
       <c r="E9" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>21/10: N1/N2 đề xuất dùng ranh giới trước sáp nhập (63 tỉnh); DimLocation chỉ lưu tỉnh cũ. Chờ nhóm xác nhận</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
@@ -4237,7 +4257,11 @@
       <c r="E10" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>21/10: đã chốt 1 mm trong (t, t+24h], nguồn Open-Meteo cho thí nghiệm đầu; ưu tiên trạm/ERA5 để sau (docs/rain-label.md). N3 chưa duyệt</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
@@ -4273,7 +4297,11 @@
       <c r="E12" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="24"/>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>21/10: ngưỡng 0,40 chọn trên 2024 theo F1 (Recall 0,82); chưa có mục tiêu Recall định lượng (đề xuất chờ duyệt)</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2131,7 +2131,7 @@
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. 21/10 N1/N2 đề xuất đổi phạm vi sang ranh giới trước sáp nhập (63 tỉnh) vì giai đoạn nghiên cứu gần như toàn bộ trước 1/7/2025; chờ nhóm xác nhận. Nguồn ứng viên và tiêu chí: task-specs §7; kế hoạch: business-requirements §5a</t>
+          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. Phạm vi đã chốt 21/10 (N2): dùng ranh giới trước sáp nhập (63 tỉnh), không làm ranh giới sau 1/7/2025, vì giai đoạn nghiên cứu gần như toàn bộ trước sáp nhập. Nguồn ứng viên và tiêu chí: docs/task-specs-weeks-2-5.md §7</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>22/10: chưa bắt đầu, trễ hạn tuần 1; thiếu ERA5 nên chưa đạt mục tiêu đa định dạng (NetCDF). Đề xuất phạm vi và thứ tự (ID 4 → ID 5 → ID 14/15) ở business-requirements §5a; chỉ tải khi N3 xác nhận phạm vi</t>
+          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. Phạm vi đã thống nhất 22/10 (N1/N2, chờ N3 xác nhận): ERA5 hourly single levels, vùng 19,5–23,5°N, 102,5–107,5°E, biến t2m, d2m, tp, sp, u10, v10, tcc, 2016–2025, NetCDF. Việc cần N3: tạo tài khoản Copernicus CDS và chấp nhận giấy phép; chưa tải khi chưa có tài khoản</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh cũ-mới: không làm theo đề xuất ranh giới trước sáp nhập, chờ nhóm xác nhận</t>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: đã chốt 21/10 chỉ dùng tỉnh trước sáp nhập, không làm ánh xạ tỉnh cũ-mới</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>21/10: N1/N2 đề xuất dùng ranh giới trước sáp nhập (63 tỉnh); DimLocation chỉ lưu tỉnh cũ. Chờ nhóm xác nhận</t>
+          <t>21/10: đã chốt (N2) dùng ranh giới trước sáp nhập (63 tỉnh); DimLocation chỉ lưu tỉnh cũ, không lưu tỉnh mới</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>21/10: ngưỡng 0,40 chọn trên 2024 theo F1 (Recall 0,82); chưa có mục tiêu Recall định lượng (đề xuất chờ duyệt)</t>
+          <t>22/10: ngưỡng 0,40 chọn trên 2024 theo F1 (Recall 0,82) là kết quả test chính thức. Thêm điểm vận hành ưu tiên Recall: Recall validation ≥ 0,85 và Precision cao nhất → 0,36 (Recall 0,88). Do N1/N2 chốt thay N3, chờ N3 duyệt</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2101,8 +2101,10 @@
       <c r="E8" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>70</v>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Tải GeoJSON địa giới Việt Nam, ranh giới TRƯỚC sáp nhập (63 tỉnh). Đổi phạm vi ngày 21/10/2026; mô tả gốc: "ranh giới sau sáp nhập 1/7/2025"</t>
+        </is>
       </c>
       <c r="G8" s="19" t="s">
         <v>14</v>
@@ -2123,15 +2125,17 @@
         <f aca="false">'Tổng quan'!$E$11+(C8-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M8" s="22" t="s">
-        <v>62</v>
+      <c r="M8" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N8" s="23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. Phạm vi đã chốt 21/10 (N2): dùng ranh giới trước sáp nhập (63 tỉnh), không làm ranh giới sau 1/7/2025, vì giai đoạn nghiên cứu gần như toàn bộ trước sáp nhập. Nguồn ứng viên và tiêu chí: docs/task-specs-weeks-2-5.md §7</t>
+          <t>22/10: scripts/ingest_boundaries.py: GeoJSON 63 tỉnh trước sáp nhập (geoBoundaries VNM ADM1, commit 9469f09, năm 2008) trong Bronze kèm manifest (SHA-256, giấy phép, CRS); Silver 25 tỉnh miền Bắc (QĐ 368, 369/QĐ-TTg), 8 tỉnh có dữ liệu. Hình học hợp lệ 64/64; 8/8 điểm nằm đúng tỉnh trong dim_location. Hạn chế: ranh giới lấy từ Wikipedia/Wikimedia, độ chi tiết thấp; giấy phép ghi Public Domain (geoBoundaries) và ODbL (HDX). Phạm vi đã chốt 21/10: không làm ranh giới sau sáp nhập</t>
         </is>
       </c>
     </row>
@@ -2461,8 +2465,10 @@
       <c r="E15" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>87</v>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>DimLocation (chỉ tỉnh trước sáp nhập; mô tả gốc "tỉnh cũ + tỉnh mới", đổi ngày 21/10/2026), DimStation, gán trạm theo khoảng cách bằng GeoPandas</t>
+        </is>
       </c>
       <c r="G15" s="19" t="s">
         <v>14</v>
@@ -2493,7 +2499,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: đã chốt 21/10 chỉ dùng tỉnh trước sáp nhập, không làm ánh xạ tỉnh cũ-mới</t>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: chỉ dùng tỉnh trước sáp nhập (đã chốt 21/10); 8 điểm đã kiểm tra nằm đúng tỉnh trên GeoJSON ID 4 (22/10)</t>
         </is>
       </c>
     </row>
@@ -4226,8 +4232,10 @@
       <c r="B9" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>206</v>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Địa điểm = điểm tọa độ; DimLocation chỉ lưu tỉnh trước sáp nhập; GeoJSON dùng ranh giới trước sáp nhập (63 tỉnh). Đổi ngày 21/10/2026; cách xử lý gốc: "DimLocation lưu cả tỉnh cũ và mới; GeoJSON dùng ranh giới mới"</t>
+        </is>
       </c>
       <c r="D9" s="19" t="s">
         <v>14</v>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -1971,11 +1971,11 @@
         </is>
       </c>
       <c r="N5" s="23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>Compose/Dockerfile build OK; MinIO+Postgres đã chạy. Chưa kiểm chứng webserver/scheduler end-to-end (21/10)</t>
+          <t>22/10: kiểm chứng đầu-cuối: webserver + scheduler healthy (/health), 2 DAG nạp không lỗi, DAG kiểm tra hệ thống chạy thành công qua REST API (cả 2 task); DW giữ nguyên sau khi khởi động lại. Kiểm chứng trên 1 máy (cả nhóm hiện là 1 người). Đủ tiêu chí, chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2023,11 +2023,11 @@
         </is>
       </c>
       <c r="N6" s="23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
-          <t>Đã có 3 bucket và key đúng quy ước. Còn thiếu: Bronze chưa giữ nguyên payload gốc (_pipeline_metadata)</t>
+          <t>22/10: 3 bucket, key đúng quy ước. Bronze Open-Meteo giữ nguyên bytes gốc + manifest (SHA-256, độ phủ, tọa độ lưới) cho cả 80 file; bỏ qua theo checksum, không theo kích thước. Còn lại: Bronze Meteostat chưa có manifest (thuộc ID 9)</t>
         </is>
       </c>
     </row>
@@ -2077,11 +2077,11 @@
         </is>
       </c>
       <c r="N7" s="23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t>22/10: DDL + sơ đồ star schema (outputs/dfd-weather-20261013, chỉ có trên máy cục bộ vì outputs/ không đưa lên Git). Đã chốt: cơ sở lịch UTC+7; prediction (sql/04, sql/05). Còn mở: nhiều trạm/nguồn trên cùng điểm</t>
+          <t>22/10: sơ đồ Star Schema sinh từ DW thật (9 bảng, 14 khóa ngoại, grain từng fact): docs/diagrams/star-schema.md; thay bản phác 13/10 chỉ có trong outputs/. Cơ sở lịch UTC+7, prediction, chọn trạm (tối đa 1 trạm/điểm) đều đã chốt. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2177,15 +2177,17 @@
         <f aca="false">'Tổng quan'!$E$11+(C9-1)*7+4</f>
         <v>46311</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>62</v>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N9" s="23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>22/10: chưa bắt đầu, trễ hạn tuần 1. Phạm vi đã thống nhất 22/10 (N1/N2, chờ N3 xác nhận): ERA5 hourly single levels, vùng 19,5–23,5°N, 102,5–107,5°E, biến t2m, d2m, tp, sp, u10, v10, tcc, 2016–2025, NetCDF. Việc cần N3: tạo tài khoản Copernicus CDS và chấp nhận giấy phép; chưa tải khi chưa có tài khoản</t>
+          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu đầu tiên chạy thành công (job 70c1b649…, xếp hàng 80 s, xử lý ~6,5 phút). Bronze có tháng 1/2024: era5_north_vietnam_hourly_202401.zip (3,8 MB, 2 file NetCDF: 6 biến tức thời + lượng mưa tp; 744 giờ; lưới 17×23 ô) kèm manifest. Chưa gửi 119 tháng còn lại của 2016–2025 (chờ bạn đồng ý)</t>
         </is>
       </c>
     </row>
@@ -2337,11 +2339,11 @@
         </is>
       </c>
       <c r="N12" s="23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>21/10: chạy lại trên máy N1/N2: 80/80 file Bronze (8 điểm × 2016–2025), 326 s; «0 lỗi» dựa trên số object vì script khi đó vẫn thoát mã 0 khi có file lỗi. 22/10: đã sửa: file lỗi → thoát mã 1 sau khi thử hết các file còn lại, chỉ thử lại lỗi 429/5xx/mạng; Silver coi file Bronze thiếu là lỗi. Còn lệch: Bronze chưa giữ nguyên payload gốc, thiếu manifest</t>
+          <t>22/10: Bronze giữ nguyên payload gốc + manifest; tải lại 80/80 file (339 s, 0 lỗi), dữ liệu theo giờ giống hệt bản cũ; Silver 2024 giống từng dòng (70.272). Chạy lại: bỏ qua 80 file theo checksum. Lỗi thoát mã 1 (sửa 22/10). Tiêu chí «SHA bằng bản tải mới» không đạt được về nguyên tắc vì phản hồi có generationtime_ms; thay bằng so sánh dữ liệu theo giờ</t>
         </is>
       </c>
     </row>
@@ -2645,13 +2647,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C18-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M18" s="22" t="s">
-        <v>62</v>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="24"/>
+        <v>60</v>
+      </c>
+      <c r="O18" s="24" t="inlineStr">
+        <is>
+          <t>22/10: scripts/ingest_era5.py đọc NetCDF bằng xarray để kiểm tra (biến, số giờ, vùng) rồi lưu Bronze nguyên bản kèm manifest; đã chạy thật cho 2024-01 (khớp yêu cầu, chạy lại bỏ qua theo checksum). Còn lại: các tháng khác</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2447,7 +2447,7 @@
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi</t>
+          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi. 22/10: file Bronze Open-Meteo bị thiếu tính là lỗi (trừ khi có --allow-missing); Silver kiểm tra SHA-256 của Bronze theo manifest; chạy lại Silver 2024 giống từng dòng (70.272)</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: station_key trong Gold lưu dạng số nguyên (đã áp dụng cho 2024; các năm khác khi nạp lại). Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn</t>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn</t>
         </is>
       </c>
     </row>
@@ -2799,13 +2799,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C21-1)*7+4</f>
         <v>46339</v>
       </c>
-      <c r="M21" s="22" t="s">
-        <v>62</v>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O21" s="24" t="inlineStr">
+        <is>
+          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): tải Open-Meteo + Meteostat → Silver → seed dim → Gold → DW → đối chiếu số dòng DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy thật: 2024 HAN (khớp 17.551 dòng), chạy lại không thêm dòng, cố ý tắt MinIO → lỗi rõ ràng rồi chạy tiếp thành công, 2024 cả 8 điểm (khớp 79.039 dòng). Lệch so với đặc tả: cửa sổ nhỏ nhất là 1 năm (script theo năm), chưa gồm GHCNh/ERA5</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="N21" s="23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): tải Open-Meteo + Meteostat → Silver → seed dim → Gold → DW → đối chiếu số dòng DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy thật: 2024 HAN (khớp 17.551 dòng), chạy lại không thêm dòng, cố ý tắt MinIO → lỗi rõ ràng rồi chạy tiếp thành công, 2024 cả 8 điểm (khớp 79.039 dòng). Lệch so với đặc tả: cửa sổ nhỏ nhất là 1 năm (script theo năm), chưa gồm GHCNh/ERA5</t>
+          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): Open-Meteo, Meteostat, mưa ngày GHCNh: tải → Silver → seed dim → Gold/DW → đối chiếu DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy: 2024 HAN, chạy lại không thêm dòng, cố ý tắt MinIO rồi chạy tiếp thành công, 2024 cả 8 điểm, và cả 2016–2025 (3 phút 43 giây; khớp 788.861 dòng giờ và 17.866 ngày mưa; không tải lại gì). Cửa sổ nhỏ nhất 1 năm × 1 điểm (đã chốt). Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2187,7 +2187,7 @@
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu đầu tiên chạy thành công (job 70c1b649…, xếp hàng 80 s, xử lý ~6,5 phút). Bronze có tháng 1/2024: era5_north_vietnam_hourly_202401.zip (3,8 MB, 2 file NetCDF: 6 biến tức thời + lượng mưa tp; 744 giờ; lưới 17×23 ô) kèm manifest. Chưa gửi 119 tháng còn lại của 2016–2025 (chờ bạn đồng ý)</t>
+          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu đầu tiên chạy thành công (job 70c1b649…, ~6,5 phút). Đã gửi yêu cầu cho 2016–2025, lần lượt từng tháng (CDS từ chối gửi nhiều yêu cầu cùng lúc). Đầu ra «yêu cầu tải đã vào hàng đợi» đã đạt; tải đủ file thuộc ID 14</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>22/10: scripts/ingest_era5.py đọc NetCDF bằng xarray để kiểm tra (biến, số giờ, vùng) rồi lưu Bronze nguyên bản kèm manifest; đã chạy thật cho 2024-01 (khớp yêu cầu, chạy lại bỏ qua theo checksum). Còn lại: các tháng khác</t>
+          <t>22/10: scripts/ingest_era5.py đọc NetCDF bằng xarray để kiểm tra (biến, số giờ, vùng) rồi lưu Bronze nguyên bản kèm manifest; chạy lại bỏ qua theo checksum. Bronze có 2016-01, 2016-02, 2024-01. Đang tải lần lượt: 2024–2025 trước (phạm vi dự phòng, business-requirements §5a), rồi 2016–2023. CDS chỉ cho 1 yêu cầu chờ mỗi lúc; một tháng chờ hàng đợi ~1 giờ 40 phút, xử lý ~4 phút, nên cần vài ngày</t>
         </is>
       </c>
     </row>
@@ -3163,13 +3163,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C28-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M28" s="22" t="s">
-        <v>62</v>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N28" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O28" s="24" t="inlineStr">
+        <is>
+          <t>22/10: scripts/quality_gate.py, task quality_gate trong DAG (sau bước Silver, trước khi ghi DW). Dừng DAG khi: thiếu cột hoặc khóa trống; giờ không UTC hoặc sai tháng; trùng nguồn × điểm × giờ; giá trị ngoài khoảng hợp lệ của data-contract; thiếu giờ Open-Meteo; GHCNh trùng ngày, sai khung 12:00 UTC, mưa ngoài 0–999 mm. Cảnh báo, không dừng (ngưỡng chốt 22/10 từ dữ liệu 2016–2025): độ phủ Meteostat &lt; 95%, GHCNh &lt; 90%; Open-Meteo thiếu giá trị; Meteostat thiếu nhiệt độ/độ ẩm &gt; 5%; nhiệt độ ngoài 0–45 °C; áp suất ngoài 950–1050 hPa; mưa giờ &gt; 100 mm; mưa ngày ≥ 300 mm chưa duyệt. Dữ liệu thật 2016–2025: 712 kiểm tra, 0 lỗi, 0 cảnh báo; DAG 2024 HAN 12/12 task; test tích hợp xác nhận task Airflow báo lỗi khi Silver sai. Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="n">
@@ -3359,7 +3365,7 @@
       </c>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. 22/10: chặn ghi đè model (model đã chấm test thì không cho ghi đè). Chọn cấu hình và ngưỡng theo F1, chưa có quy tắc ưu tiên Recall (đề xuất chờ duyệt). Do N1/N2 làm thay N3</t>
+          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. 22/10: chặn ghi đè model (model đã chấm test thì không cho ghi đè). Chọn cấu hình và ngưỡng theo F1. Quy tắc ưu tiên Recall đã chốt 22/10: ngưỡng 0,36 (Recall validation 0,88); 0,40 vẫn là kết quả test chính thức. Chờ N3 duyệt (rain-label.md). Do N1/N2 làm thay N3</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4165,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>22/10: ID 5 chưa bắt đầu; đề xuất phạm vi và thứ tự ở docs/business-requirements.md §5a</t>
+          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép, tải theo tháng. Thực tế: một tháng chờ hàng đợi ~1 giờ 40 phút; CDS từ chối gửi nhiều yêu cầu cùng lúc. Đang tải 2024–2025 trước rồi 2016–2023, cần vài ngày (ID 5, 14)</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2183,11 +2183,11 @@
         </is>
       </c>
       <c r="N9" s="23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu đầu tiên chạy thành công (job 70c1b649…, ~6,5 phút). Đã gửi yêu cầu cho 2016–2025, lần lượt từng tháng (CDS từ chối gửi nhiều yêu cầu cùng lúc). Đầu ra «yêu cầu tải đã vào hàng đợi» đã đạt; tải đủ file thuộc ID 14</t>
+          <t>23/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu theo vùng miền Bắc chạy được (job 70c1b649…), nhưng mỗi tháng chờ hàng đợi ~2 giờ và CDS chỉ nhận 1 yêu cầu chờ mỗi lúc. Đã chốt 23/10: dùng ERA5 time-series (cùng dữ liệu ERA5 theo giờ, ô lưới gần nhất của 8 điểm): 8 yêu cầu 2016–2025 xong trong 320 giây. Tải theo vùng vẫn chạy tiếp cho 2024–2025 để làm minh chứng. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2653,11 +2653,11 @@
         </is>
       </c>
       <c r="N18" s="23" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>22/10: scripts/ingest_era5.py đọc NetCDF bằng xarray để kiểm tra (biến, số giờ, vùng) rồi lưu Bronze nguyên bản kèm manifest; chạy lại bỏ qua theo checksum. Bronze có 2016-01, 2016-02, 2024-01. Đang tải lần lượt: 2024–2025 trước (phạm vi dự phòng, business-requirements §5a), rồi 2016–2023. CDS chỉ cho 1 yêu cầu chờ mỗi lúc; một tháng chờ hàng đợi ~1 giờ 40 phút, xử lý ~4 phút, nên cần vài ngày</t>
+          <t>23/10: Bronze có ERA5 NetCDF nguyên bản kèm manifest: chuỗi theo giờ 8 điểm × 2016–2025 (87.672 giờ mỗi điểm, ô lưới gần nhất; scripts/ingest_era5_timeseries.py), đọc và kiểm tra bằng xarray; khớp với file theo vùng tháng 1–2/2024 tại cùng ô lưới. Theo vùng: 2016-01, 2016-02, 2024-01, 2024-02, đang tải tiếp 2024–2025. Chạy lại: bỏ qua theo checksum. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>
@@ -2699,13 +2699,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C19-1)*7+4</f>
         <v>46325</v>
       </c>
-      <c r="M19" s="22" t="s">
-        <v>62</v>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N19" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O19" s="24" t="inlineStr">
+        <is>
+          <t>23/10: scripts/transform_era5_to_silver.py: K → °C, Pa → hPa, m → mm, gió từ u/v (tốc độ và hướng gió thổi đến), mây 0–1 → %, độ ẩm tính từ nhiệt độ và điểm sương (công thức Magnus); ô lưới gần nhất ghi ở grid_latitude/grid_longitude. Mưa ERA5 theo giờ đã là tổng từng giờ nên không cần khử cộng dồn (chỉ ERA5-Land cần). 701.376 dòng, 0 giá trị bị loại. So sánh với Open-Meteo (scripts/compare_era5_open_meteo.py): nhiệt độ tương quan 0,96–0,98; áp suất ở LCA, HBI lệch nhiều do độ cao ô lưới. Chưa nạp ERA5 vào DW (chưa quyết định). Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="n">
@@ -4165,7 +4171,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>22/10: đã đăng ký CDS, chấp nhận giấy phép, tải theo tháng. Thực tế: một tháng chờ hàng đợi ~1 giờ 40 phút; CDS từ chối gửi nhiều yêu cầu cùng lúc. Đang tải 2024–2025 trước rồi 2016–2023, cần vài ngày (ID 5, 14)</t>
+          <t>23/10: chuyển sang ERA5 time-series theo điểm: 8 điểm × 2016–2025 xong trong 320 giây. Tải theo vùng (mỗi tháng chờ ~2 giờ) chỉ tiếp tục cho 2024–2025 (ID 5, 14)</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4191,11 @@
       <c r="E5" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="24"/>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>23/10: đã đổi đơn vị ở Silver (scripts/transform_era5_to_silver.py), tính gió từ u/v, lấy ô lưới gần nhất. Sản phẩm là ERA5 (không phải ERA5-Land): mưa theo giờ đã là tổng từng giờ, không cần khử cộng dồn</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
@@ -4203,7 +4213,11 @@
       <c r="E6" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="24"/>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>23/10: so sánh ERA5 – Open-Meteo 2016–2025 (scripts/compare_era5_open_meteo.py): hai nguồn không trùng hẳn; nhiệt độ lệch −1,6…+0,9 °C, tương quan 0,96–0,98; mưa năm LCA 2.064 mm (ERA5) so với 2.950 mm (Open-Meteo). Không coi là xác nhận độc lập</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2761,7 +2761,7 @@
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn</t>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn 23/10: Gold mỗi tháng gồm cả ERA5 (3 nguồn: Open-Meteo, Meteostat, ERA5). Chưa có bảng pivot đa nguồn cho ML.</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): Open-Meteo, Meteostat, mưa ngày GHCNh: tải → Silver → seed dim → Gold/DW → đối chiếu DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy: 2024 HAN, chạy lại không thêm dòng, cố ý tắt MinIO rồi chạy tiếp thành công, 2024 cả 8 điểm, và cả 2016–2025 (3 phút 43 giây; khớp 788.861 dòng giờ và 17.866 ngày mưa; không tải lại gì). Cửa sổ nhỏ nhất 1 năm × 1 điểm (đã chốt). Chờ bạn xác nhận Hoàn thành</t>
+          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): Open-Meteo, Meteostat, mưa ngày GHCNh: tải → Silver → seed dim → Gold/DW → đối chiếu DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy: 2024 HAN, chạy lại không thêm dòng, cố ý tắt MinIO rồi chạy tiếp thành công, 2024 cả 8 điểm, và cả 2016–2025 (3 phút 43 giây; khớp 788.861 dòng giờ và 17.866 ngày mưa; không tải lại gì). Cửa sổ nhỏ nhất 1 năm × 1 điểm (đã chốt). Chờ bạn xác nhận Hoàn thành 23/10: thêm nhánh ERA5 (tải time-series → Silver) trước bước quality_gate. Chạy 2016–2025: 14/14 task thành công (lần đầu bước ERA5 lỗi vì container Airflow chưa có khóa CDS; đã sửa, chạy tiếp từ bước lỗi); đối chiếu 1.490.237 = 1.490.237 dòng giờ, 17.866 = 17.866 ngày mưa.</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; lần nạp cuối 292 s (bản trước ghi 3.493 s là sai). 22/10: phạm vi xóa khi nạp lại tính theo phạm vi yêu cầu (nguồn biến mất bị xóa; thiếu file Silver Open-Meteo của một vị trí thì tháng đó báo lỗi); thêm pressure_type (sql/05). Chạy lại 2024 trên trạng thái hiện tại: 79.039 dòng, không đổi. Bản 994.145 dòng trên máy bacnx đã lỗi thời</t>
+          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; lần nạp cuối 292 s (bản trước ghi 3.493 s là sai). 22/10: phạm vi xóa khi nạp lại tính theo phạm vi yêu cầu (nguồn biến mất bị xóa; thiếu file Silver Open-Meteo của một vị trí thì tháng đó báo lỗi); thêm pressure_type (sql/05). Chạy lại 2024 trên trạng thái hiện tại: 79.039 dòng, không đổi. Bản 994.145 dòng trên máy bacnx đã lỗi thời 23/10: nạp thêm ERA5 701.376 dòng (đã chốt nạp ERA5 theo đề cương §8, §10); DW 1.490.237 dòng, 0 trùng khóa; Open-Meteo, Meteostat, mưa ngày, dự báo không đổi.</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>22/10: scripts/quality_gate.py, task quality_gate trong DAG (sau bước Silver, trước khi ghi DW). Dừng DAG khi: thiếu cột hoặc khóa trống; giờ không UTC hoặc sai tháng; trùng nguồn × điểm × giờ; giá trị ngoài khoảng hợp lệ của data-contract; thiếu giờ Open-Meteo; GHCNh trùng ngày, sai khung 12:00 UTC, mưa ngoài 0–999 mm. Cảnh báo, không dừng (ngưỡng chốt 22/10 từ dữ liệu 2016–2025): độ phủ Meteostat &lt; 95%, GHCNh &lt; 90%; Open-Meteo thiếu giá trị; Meteostat thiếu nhiệt độ/độ ẩm &gt; 5%; nhiệt độ ngoài 0–45 °C; áp suất ngoài 950–1050 hPa; mưa giờ &gt; 100 mm; mưa ngày ≥ 300 mm chưa duyệt. Dữ liệu thật 2016–2025: 712 kiểm tra, 0 lỗi, 0 cảnh báo; DAG 2024 HAN 12/12 task; test tích hợp xác nhận task Airflow báo lỗi khi Silver sai. Chờ bạn xác nhận Hoàn thành</t>
+          <t>22/10: scripts/quality_gate.py, task quality_gate trong DAG (sau bước Silver, trước khi ghi DW). Dừng DAG khi: thiếu cột hoặc khóa trống; giờ không UTC hoặc sai tháng; trùng nguồn × điểm × giờ; giá trị ngoài khoảng hợp lệ của data-contract; thiếu giờ Open-Meteo; GHCNh trùng ngày, sai khung 12:00 UTC, mưa ngoài 0–999 mm. Cảnh báo, không dừng (ngưỡng chốt 22/10 từ dữ liệu 2016–2025): độ phủ Meteostat &lt; 95%, GHCNh &lt; 90%; Open-Meteo thiếu giá trị; Meteostat thiếu nhiệt độ/độ ẩm &gt; 5%; nhiệt độ ngoài 0–45 °C; áp suất ngoài 950–1050 hPa; mưa giờ &gt; 100 mm; mưa ngày ≥ 300 mm chưa duyệt. Dữ liệu thật 2016–2025: 712 kiểm tra, 0 lỗi, 0 cảnh báo; DAG 2024 HAN 12/12 task; test tích hợp xác nhận task Airflow báo lỗi khi Silver sai. Chờ bạn xác nhận Hoàn thành 23/10: kiểm tra cả ERA5 (bắt buộc đủ giờ; cảnh báo áp suất ngoài 900–1050 hPa vì ô lưới cao hơn điểm): 1.032 kiểm tra, 0 lỗi, 0 cảnh báo.</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3759,13 +3759,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C40-1)*7+4</f>
         <v>46367</v>
       </c>
-      <c r="M40" s="22" t="s">
-        <v>62</v>
+      <c r="M40" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N40" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O40" s="24" t="inlineStr">
+        <is>
+          <t>23/10: scripts/analyze_cart_thresholds.py → gold/ml_models/cart_rain_next24h_v1/threshold_error_analysis.json. So sánh ngưỡng trên validation 2024 (lưới 0,30–0,70 của quy tắc chọn ngưỡng): quy tắc F1 vẫn ra 0,40 (ngưỡng chính thức), quy tắc ưu tiên Recall ra 0,36. Test 2025 chỉ tính ở các ngưỡng đã chốt (phân tích sau, có ghi rõ): 0,40 → P 0,762 / R 0,792 / F1 0,777; 0,36 → 0,723 / 0,848 / 0,780 (thêm 2.709 báo động giả, bớt 1.945 ca bỏ sót). Lỗi: bỏ sót nhiều nhất ở mưa nhẹ 1–2 mm (42%); báo động giả phần lớn là cửa sổ có 0–1 mm; mưa sau 24 giờ khô chỉ bắt được 17%; mùa mưa F1 0,836, mùa khô 0,624. Chi tiết: rain-label.md. Do N1/N2 làm thay N3. Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3269,13 +3269,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C30-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M30" s="22" t="s">
-        <v>62</v>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N30" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="O30" s="24" t="inlineStr">
+        <is>
+          <t>23/10: đo thật bằng scripts/benchmark_dw_queries.py (EXPLAIN ANALYZE, 3 lần, trung vị) trên DW 1.490.237 dòng: nạp từng view cho dashboard 0,3–1,3 giây, tổng khoảng 5,8 giây; truy vấn đối chiếu 0,4 ms–1,2 giây. Index hiện có đã đủ cho truy vấn có lọc; đã thử thêm index ghép và index cho 4 khóa ngoại trong giao dịch rồi hoàn tác: không nhanh hơn (view tổng hợp phải quét cả bảng), nên không thêm. Đề xuất mục tiêu: mỗi view dưới 5 giây, truy vấn đối chiếu dưới 2 giây (đang đạt). Chờ bạn chốt mục tiêu</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3275,11 +3275,11 @@
         </is>
       </c>
       <c r="N30" s="23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O30" s="24" t="inlineStr">
         <is>
-          <t>23/10: đo thật bằng scripts/benchmark_dw_queries.py (EXPLAIN ANALYZE, 3 lần, trung vị) trên DW 1.490.237 dòng: nạp từng view cho dashboard 0,3–1,3 giây, tổng khoảng 5,8 giây; truy vấn đối chiếu 0,4 ms–1,2 giây. Index hiện có đã đủ cho truy vấn có lọc; đã thử thêm index ghép và index cho 4 khóa ngoại trong giao dịch rồi hoàn tác: không nhanh hơn (view tổng hợp phải quét cả bảng), nên không thêm. Đề xuất mục tiêu: mỗi view dưới 5 giây, truy vấn đối chiếu dưới 2 giây (đang đạt). Chờ bạn chốt mục tiêu</t>
+          <t>23/10: đo thật bằng scripts/benchmark_dw_queries.py (EXPLAIN ANALYZE, 3 lần, trung vị) trên DW 1.490.237 dòng: nạp từng view cho dashboard 0,3–1,3 giây, tổng khoảng 5,8 giây; truy vấn đối chiếu 0,4 ms–1,2 giây. Index hiện có đã đủ cho truy vấn có lọc; đã thử thêm index ghép và index cho 4 khóa ngoại trong giao dịch rồi hoàn tác: không nhanh hơn (view tổng hợp phải quét cả bảng), nên không thêm. Mục tiêu đã chốt 23/10: mỗi view dưới 5 giây, truy vấn đối chiếu dưới 2 giây (đang đạt: tối đa 1,3 giây và 1,2 giây). Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3579,13 +3579,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C36-1)*7+4</f>
         <v>46360</v>
       </c>
-      <c r="M36" s="22" t="s">
-        <v>62</v>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N36" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>23/10: DAG weather_rain_scoring_dag (chạy tay): kiểm tra khoảng ngày → chấm điểm (scripts/score_cart.py: kiểm tra SHA-256 của mô hình, tính lại đặc trưng từ Silver, thiếu dữ liệu thì báo lỗi) → ghi Gold mỗi ngày một file → đăng lên DW (scripts/publish_predictions.py: chỉ ghi dòng thay đổi) → đối chiếu DW với Gold. Chỉ đăng dự báo tập test 2025 (01/01–30/12, mục tiêu không sang 2026). Chạy thật cả năm 2025: 4/4 task thành công trong 40 giây, 69.888 dự báo, DW không đổi dòng nào (mã băm trước và sau giống hệt); thử khoảng ngày sai thì DAG dừng ngay ở bước đầu. Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3221,13 +3221,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C29-1)*7+4</f>
         <v>46353</v>
       </c>
-      <c r="M29" s="22" t="s">
-        <v>62</v>
+      <c r="M29" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O29" s="24" t="inlineStr">
+        <is>
+          <t>23/10: DAG weather_incremental_dag chạy theo lịch hằng ngày (không chạy bù quá khứ, tạm dừng khi mới tạo): đọc mốc watermark trong MinIO (năm cuối đã nạp và đối chiếu xong) → chọn năm mới tiếp theo + chạy lại 1 năm trước để lấy dữ liệu sửa muộn, không vượt quá 2025 → gọi DAG Bronze→DW (task 17) và chờ → chỉ dời mốc khi lần chạy đó thành công. Chạy thật: đặt mốc 2024, lần chạy theo lịch xử lý 2024–2025 (14/14 task, 3 phút, đối chiếu 298.192 = 298.192 dòng giờ), mốc dời lên 2025; DW giống hệt trước khi chạy (không trùng, không đổi giá trị); lần chạy sau tự bỏ qua vì đã đủ đến 2025. Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2395,7 +2395,7 @@
       </c>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. 22/10: trạm Meteostat 48820 thực chất là sân bay Nội Bài (cách điểm HAN 22 km), đã ghi lại; quy tắc cực trị so sánh theo độ phân giải 0,1 mm. Bronze Meteostat lưu CSV đã giải nén, chưa có manifest/SHA. Chờ nhóm duyệt quy tắc cực trị 300 mm</t>
+          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. 22/10: trạm Meteostat 48820 thực chất là sân bay Nội Bài (cách điểm HAN 22 km), đã ghi lại; quy tắc cực trị so sánh theo độ phân giải 0,1 mm. Bronze Meteostat lưu CSV đã giải nén, chưa có manifest/SHA. Chờ nhóm duyệt quy tắc cực trị 300 mm 23/10: Bronze Meteostat lưu nguyên file .csv.gz nhận về kèm manifest (SHA-256, URL, thời điểm tải); 15 file CSV cũ được thay sau khi kiểm tra bản tải mới giải nén giống hệt từng byte; 25 năm-trạm không có dữ liệu (HTTP 404) được ghi lại nên lần sau không hỏi lại. Silver Meteostat kiểm tra SHA-256, chạy lại giống hệt (120 file, 87.485 dòng); DW không đổi. Chạy chuỗi DAG 2024 × HAN trong container không có Internet: 13/13 bước thành công.</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2497,11 +2497,11 @@
         </is>
       </c>
       <c r="N15" s="23" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: chỉ dùng tỉnh trước sáp nhập (đã chốt 21/10); 8 điểm đã kiểm tra nằm đúng tỉnh trên GeoJSON ID 4 (22/10)</t>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: chỉ dùng tỉnh trước sáp nhập (đã chốt 21/10); 8 điểm đã kiểm tra nằm đúng tỉnh trên GeoJSON ID 4 (22/10) 23/10: gán trạm bằng GeoPandas (scripts/assign_stations_geo.py): tính khoảng cách trên hệ tọa độ UTM 48N, trạm gần nhất trong 30 km, kiểm tra tỉnh của điểm và trạm, so với bảng trạm và dim_station (chỉ đọc). Kết quả đạt: trạm mưa GHCNh = trạm gần nhất ở cả 8 điểm; Meteostat HAN dùng Nội Bài (21,9 km) dù Hà Đông gần hơn (11,4 km, chưa chốt cho Meteostat); khoảng cách lưu lệch tối đa 0,14 km do tính trên hình cầu; 8/8 điểm đúng tỉnh. Tọa độ trạm Nội Bài nằm trong Vĩnh Phúc 2,5 km theo bản đồ geoBoundaries (chưa xác minh, không ảnh hưởng dữ liệu). DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2443,11 +2443,11 @@
         </is>
       </c>
       <c r="N14" s="23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi. 22/10: file Bronze Open-Meteo bị thiếu tính là lỗi (trừ khi có --allow-missing); Silver kiểm tra SHA-256 của Bronze theo manifest; chạy lại Silver 2024 giống từng dòng (70.272)</t>
+          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi. 22/10: file Bronze Open-Meteo bị thiếu tính là lỗi (trừ khi có --allow-missing); Silver kiểm tra SHA-256 của Bronze theo manifest; chạy lại Silver 2024 giống từng dòng (70.272) 23/10: Silver Open-Meteo lưu thêm tọa độ và độ cao ô lưới API trả về (grid_latitude, grid_longitude, grid_elevation_m) và báo lỗi nếu dữ liệu không ở UTC (utc_offset_seconds khác 0). Chạy lại 2016–2025: 80 file đều ở UTC, 701.376 dòng, các cột cũ giống hệt; quality gate 1.032 kiểm tra 0 lỗi; nạp lại Gold, đối chiếu 1.490.237 = 1.490.237; DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="N20" s="23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn 23/10: Gold mỗi tháng gồm cả ERA5 (3 nguồn: Open-Meteo, Meteostat, ERA5). Chưa có bảng pivot đa nguồn cho ML.</t>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn 23/10: Gold mỗi tháng gồm cả ERA5 (3 nguồn: Open-Meteo, Meteostat, ERA5). Chưa có bảng pivot đa nguồn cho ML. 23/10: bảng Gold ML gộp nguồn (scripts/build_ml_pivot.py, gold/ml_pivot/weather_hourly_by_source_v1): mỗi dòng là một điểm × một giờ UTC, mỗi nguồn có cột riêng cho 8 biến (24 cột), không cộng gộp giữa các nguồn, thiếu thì để trống. 2016–2025: 701.376 dòng; số dòng, số giá trị và tổng từng cột khớp Gold, số dòng từng nguồn × năm khớp DW. Có manifest ghi nguồn gốc (SHA-256 các file Gold). Mô hình CART v1 không dùng bảng này; DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -3685,13 +3685,19 @@
         <f aca="false">'Tổng quan'!$E$11+(C38-1)*7+4</f>
         <v>46367</v>
       </c>
-      <c r="M38" s="22" t="s">
-        <v>62</v>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>Đang làm</t>
+        </is>
       </c>
       <c r="N38" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="24"/>
+        <v>95</v>
+      </c>
+      <c r="O38" s="24" t="inlineStr">
+        <is>
+          <t>23/10: chạy lại toàn bộ trên môi trường sạch (clone repo mới, volume Docker trống, tải lại mọi nguồn): DAG Bronze→DW 14/14 bước ngay lần đầu, 15 phút; kiểm tra chất lượng 1.032 lượt 0 lỗi; đối chiếu 1.490.237 dòng giờ, 17.866 ngày mưa. So với máy hiện tại: mọi bảng DW khớp theo khóa tự nhiên; Silver/Gold khớp từng byte; chỉ khác dấu thời gian tải và ID tự tăng. Huấn luyện lại ra đúng mô hình v1 (cùng SHA-256). Chạy lại và chạy lỗi đều đúng. Tìm ra và đã sửa 1 lỗi: trên máy mới, lệnh huấn luyện mặc định có thể lưu mô hình khác dưới tên v1; giờ v1 được ghim SHA-256 và có gói phát hành (scripts/model_release.py). Hướng dẫn: docs/reproduce-from-scratch.md. Chờ bạn xác nhận Hoàn thành</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="n">

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -1967,15 +1967,15 @@
       </c>
       <c r="M5" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N5" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O5" s="24" t="inlineStr">
         <is>
-          <t>22/10: kiểm chứng đầu-cuối: webserver + scheduler healthy (/health), 2 DAG nạp không lỗi, DAG kiểm tra hệ thống chạy thành công qua REST API (cả 2 task); DW giữ nguyên sau khi khởi động lại. Kiểm chứng trên 1 máy (cả nhóm hiện là 1 người). Đủ tiêu chí, chờ bạn xác nhận Hoàn thành</t>
+          <t>22/10: kiểm chứng đầu-cuối: webserver + scheduler healthy (/health), 2 DAG nạp không lỗi, DAG kiểm tra hệ thống chạy thành công qua REST API (cả 2 task); DW giữ nguyên sau khi khởi động lại. Kiểm chứng trên 1 máy (cả nhóm hiện là 1 người). Đủ tiêu chí. 23/10: dựng lại từ đầu trên môi trường sạch thành công (task 34). Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2019,15 +2019,15 @@
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N6" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
-          <t>22/10: 3 bucket, key đúng quy ước. Bronze Open-Meteo giữ nguyên bytes gốc + manifest (SHA-256, độ phủ, tọa độ lưới) cho cả 80 file; bỏ qua theo checksum, không theo kích thước. Còn lại: Bronze Meteostat chưa có manifest (thuộc ID 9)</t>
+          <t>22/10: 3 bucket, key đúng quy ước. Bronze Open-Meteo giữ nguyên bytes gốc + manifest (SHA-256, độ phủ, tọa độ lưới) cho cả 80 file; bỏ qua theo checksum, không theo kích thước. Còn lại: Bronze Meteostat chưa có manifest (thuộc ID 9). 23/10: Bronze Meteostat đã có manifest (task 9), phần còn lại đã xong. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2073,15 +2073,15 @@
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N7" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O7" s="24" t="inlineStr">
         <is>
-          <t>22/10: sơ đồ Star Schema sinh từ DW thật (9 bảng, 14 khóa ngoại, grain từng fact): docs/diagrams/star-schema.md; thay bản phác 13/10 chỉ có trong outputs/. Cơ sở lịch UTC+7, prediction, chọn trạm (tối đa 1 trạm/điểm) đều đã chốt. Chờ bạn xác nhận Hoàn thành</t>
+          <t>22/10: sơ đồ Star Schema sinh từ DW thật (9 bảng, 14 khóa ngoại, grain từng fact): docs/diagrams/star-schema.md; thay bản phác 13/10 chỉ có trong outputs/. Cơ sở lịch UTC+7, prediction, chọn trạm (tối đa 1 trạm/điểm) đều đã chốt. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2127,15 +2127,15 @@
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N8" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
-          <t>22/10: scripts/ingest_boundaries.py: GeoJSON 63 tỉnh trước sáp nhập (geoBoundaries VNM ADM1, commit 9469f09, năm 2008) trong Bronze kèm manifest (SHA-256, giấy phép, CRS); Silver 25 tỉnh miền Bắc (QĐ 368, 369/QĐ-TTg), 8 tỉnh có dữ liệu. Hình học hợp lệ 64/64; 8/8 điểm nằm đúng tỉnh trong dim_location. Hạn chế: ranh giới lấy từ Wikipedia/Wikimedia, độ chi tiết thấp; giấy phép ghi Public Domain (geoBoundaries) và ODbL (HDX). Phạm vi đã chốt 21/10: không làm ranh giới sau sáp nhập</t>
+          <t>22/10: scripts/ingest_boundaries.py: GeoJSON 63 tỉnh trước sáp nhập (geoBoundaries VNM ADM1, commit 9469f09, năm 2008) trong Bronze kèm manifest (SHA-256, giấy phép, CRS); Silver 25 tỉnh miền Bắc (QĐ 368, 369/QĐ-TTg), 8 tỉnh có dữ liệu. Hình học hợp lệ 64/64; 8/8 điểm nằm đúng tỉnh trong dim_location. Hạn chế: ranh giới lấy từ Wikipedia/Wikimedia, độ chi tiết thấp; giấy phép ghi Public Domain (geoBoundaries) và ODbL (HDX). Phạm vi đã chốt 21/10: không làm ranh giới sau sáp nhập. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2179,15 +2179,15 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N9" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O9" s="24" t="inlineStr">
         <is>
-          <t>23/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu theo vùng miền Bắc chạy được (job 70c1b649…), nhưng mỗi tháng chờ hàng đợi ~2 giờ và CDS chỉ nhận 1 yêu cầu chờ mỗi lúc. Đã chốt 23/10: dùng ERA5 time-series (cùng dữ liệu ERA5 theo giờ, ô lưới gần nhất của 8 điểm): 8 yêu cầu 2016–2025 xong trong 320 giây. Tải theo vùng vẫn chạy tiếp cho 2024–2025 để làm minh chứng. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: đã đăng ký CDS, chấp nhận giấy phép ERA5; yêu cầu theo vùng miền Bắc chạy được (job 70c1b649…), nhưng mỗi tháng chờ hàng đợi ~2 giờ và CDS chỉ nhận 1 yêu cầu chờ mỗi lúc. Đã chốt 23/10: dùng ERA5 time-series (cùng dữ liệu ERA5 theo giờ, ô lưới gần nhất của 8 điểm): 8 yêu cầu 2016–2025 xong trong 320 giây. Tải theo vùng vẫn chạy tiếp cho 2024–2025 để làm minh chứng. 23/10: đã dừng tải theo vùng; giữ 4 tháng (2016-01, 2016-02, 2024-01, 2024-02) làm minh chứng, dữ liệu dùng bản time-series. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2335,15 +2335,15 @@
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N12" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t>22/10: Bronze giữ nguyên payload gốc + manifest; tải lại 80/80 file (339 s, 0 lỗi), dữ liệu theo giờ giống hệt bản cũ; Silver 2024 giống từng dòng (70.272). Chạy lại: bỏ qua 80 file theo checksum. Lỗi thoát mã 1 (sửa 22/10). Tiêu chí «SHA bằng bản tải mới» không đạt được về nguyên tắc vì phản hồi có generationtime_ms; thay bằng so sánh dữ liệu theo giờ</t>
+          <t>22/10: Bronze giữ nguyên payload gốc + manifest; tải lại 80/80 file (339 s, 0 lỗi), dữ liệu theo giờ giống hệt bản cũ; Silver 2024 giống từng dòng (70.272). Chạy lại: bỏ qua 80 file theo checksum. Lỗi thoát mã 1 (sửa 22/10). Tiêu chí «SHA bằng bản tải mới» không đạt được về nguyên tắc vì phản hồi có generationtime_ms; thay bằng so sánh dữ liệu theo giờ. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2439,15 +2439,15 @@
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N14" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O14" s="24" t="inlineStr">
         <is>
-          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi. 22/10: file Bronze Open-Meteo bị thiếu tính là lỗi (trừ khi có --allow-missing); Silver kiểm tra SHA-256 của Bronze theo manifest; chạy lại Silver 2024 giống từng dòng (70.272) 23/10: Silver Open-Meteo lưu thêm tọa độ và độ cao ô lưới API trả về (grid_latitude, grid_longitude, grid_elevation_m) và báo lỗi nếu dữ liệu không ở UTC (utc_offset_seconds khác 0). Chạy lại 2016–2025: 80 file đều ở UTC, 701.376 dòng, các cột cũ giống hệt; quality gate 1.032 kiểm tra 0 lỗi; nạp lại Gold, đối chiếu 1.490.237 = 1.490.237; DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
+          <t>21/10: Silver chạy lại: Open-Meteo 701.376 dòng; Meteostat 87.485 dòng sau khi loại 436.502 giá trị mô hình và 43.575 dòng không có quan trắc; 60 file Silver cũ đã xóa; 0 xung đột, 0 lỗi. 22/10: file Bronze Open-Meteo bị thiếu tính là lỗi (trừ khi có --allow-missing); Silver kiểm tra SHA-256 của Bronze theo manifest; chạy lại Silver 2024 giống từng dòng (70.272) 23/10: Silver Open-Meteo lưu thêm tọa độ và độ cao ô lưới API trả về (grid_latitude, grid_longitude, grid_elevation_m) và báo lỗi nếu dữ liệu không ở UTC (utc_offset_seconds khác 0). Chạy lại 2016–2025: 80 file đều ở UTC, 701.376 dòng, các cột cũ giống hệt; quality gate 1.032 kiểm tra 0 lỗi; nạp lại Gold, đối chiếu 1.490.237 = 1.490.237; DW không đổi. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2493,15 +2493,15 @@
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N15" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: chỉ dùng tỉnh trước sáp nhập (đã chốt 21/10); 8 điểm đã kiểm tra nằm đúng tỉnh trên GeoJSON ID 4 (22/10) 23/10: gán trạm bằng GeoPandas (scripts/assign_stations_geo.py): tính khoảng cách trên hệ tọa độ UTM 48N, trạm gần nhất trong 30 km, kiểm tra tỉnh của điểm và trạm, so với bảng trạm và dim_station (chỉ đọc). Kết quả đạt: trạm mưa GHCNh = trạm gần nhất ở cả 8 điểm; Meteostat HAN dùng Nội Bài (21,9 km) dù Hà Đông gần hơn (11,4 km, chưa chốt cho Meteostat); khoảng cách lưu lệch tối đa 0,14 km do tính trên hình cầu; 8/8 điểm đúng tỉnh. Tọa độ trạm Nội Bài nằm trong Vĩnh Phúc 2,5 km theo bản đồ geoBoundaries (chưa xác minh, không ảnh hưởng dữ liệu). DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
+          <t>21/10: mã/tọa độ trạm đã xác minh (Meteostat + NOAA ISD). Hợp lệ: HAN 48820, HPH 48826, TNG 48831, LCA 48803; dim_station 12 trạm (thêm 48823 Nam Định cho mưa ngày). 22/10: 48820 = sân bay Nội Bài (22,0 km, vai trò nearest_available); thêm station_role, distance_km (sql/05). Khoảng cách tính bằng haversine, không dùng GeoPandas. Tỉnh: chỉ dùng tỉnh trước sáp nhập (đã chốt 21/10); 8 điểm đã kiểm tra nằm đúng tỉnh trên GeoJSON ID 4 (22/10) 23/10: gán trạm bằng GeoPandas (scripts/assign_stations_geo.py): tính khoảng cách trên hệ tọa độ UTM 48N, trạm gần nhất trong 30 km, kiểm tra tỉnh của điểm và trạm, so với bảng trạm và dim_station (chỉ đọc). Kết quả đạt: trạm mưa GHCNh = trạm gần nhất ở cả 8 điểm; Meteostat HAN dùng Nội Bài (21,9 km) dù Hà Đông gần hơn (11,4 km, chưa chốt cho Meteostat); khoảng cách lưu lệch tối đa 0,14 km do tính trên hình cầu; 8/8 điểm đúng tỉnh. Tọa độ trạm Nội Bài nằm trong Vĩnh Phúc 2,5 km theo bản đồ geoBoundaries (chưa xác minh, không ảnh hưởng dữ liệu). DW không đổi. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2545,15 +2545,15 @@
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N16" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>dim_date 4.018 ngày, seed chạy lại ổn. Cơ sở lịch UTC+7 đã chốt 21/10 (data-contract, warehouse-schema; nhóm xác nhận qua N1/N2)</t>
+          <t>dim_date 4.018 ngày, seed chạy lại ổn. Cơ sở lịch UTC+7 đã chốt 21/10 (data-contract, warehouse-schema; nhóm xác nhận qua N1/N2). Hạn chế còn lại: dim_source ghi tần suất cập nhật của ERA5 là "Monthly Bulk" (thực tế tải time-series một lần); chưa sửa để giữ nguyên dữ liệu DW đã gửi Power BI. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2597,15 +2597,15 @@
       </c>
       <c r="M17" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N17" s="23" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>DDL chạy được trên Postgres; migration cho DB đã tồn tại: sql/02–05, chạy lại an toàn. 22/10: test tích hợp chạy đúng thứ tự khởi tạo thật (init + 02→05); sửa chú thích day_of_week (ISO) và period_of_day</t>
+          <t>DDL chạy được trên Postgres; migration cho DB đã tồn tại: sql/02–05, chạy lại an toàn. 22/10: test tích hợp chạy đúng thứ tự khởi tạo thật (init + 02→05); sửa chú thích day_of_week (ISO) và period_of_day. 23/10: DDL và migration 02–05 dựng DW mới thành công trên môi trường sạch (task 34). Hạn chế: tên database cố định weather_dwh. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2649,15 +2649,15 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N18" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O18" s="24" t="inlineStr">
         <is>
-          <t>23/10: Bronze có ERA5 NetCDF nguyên bản kèm manifest: chuỗi theo giờ 8 điểm × 2016–2025 (87.672 giờ mỗi điểm, ô lưới gần nhất; scripts/ingest_era5_timeseries.py), đọc và kiểm tra bằng xarray; khớp với file theo vùng tháng 1–2/2024 tại cùng ô lưới. Theo vùng: 2016-01, 2016-02, 2024-01, 2024-02, đang tải tiếp 2024–2025. Chạy lại: bỏ qua theo checksum. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: Bronze có ERA5 NetCDF nguyên bản kèm manifest: chuỗi theo giờ 8 điểm × 2016–2025 (87.672 giờ mỗi điểm, ô lưới gần nhất; scripts/ingest_era5_timeseries.py), đọc và kiểm tra bằng xarray; khớp với file theo vùng tháng 1–2/2024 tại cùng ô lưới. Theo vùng: 2016-01, 2016-02, 2024-01, 2024-02, đang tải tiếp 2024–2025. Chạy lại: bỏ qua theo checksum. 23/10: đã dừng tải theo vùng, giữ 4 tháng làm minh chứng. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N19" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O19" s="24" t="inlineStr">
         <is>
-          <t>23/10: scripts/transform_era5_to_silver.py: K → °C, Pa → hPa, m → mm, gió từ u/v (tốc độ và hướng gió thổi đến), mây 0–1 → %, độ ẩm tính từ nhiệt độ và điểm sương (công thức Magnus); ô lưới gần nhất ghi ở grid_latitude/grid_longitude. Mưa ERA5 theo giờ đã là tổng từng giờ nên không cần khử cộng dồn (chỉ ERA5-Land cần). 701.376 dòng, 0 giá trị bị loại. So sánh với Open-Meteo (scripts/compare_era5_open_meteo.py): nhiệt độ tương quan 0,96–0,98; áp suất ở LCA, HBI lệch nhiều do độ cao ô lưới. Chưa nạp ERA5 vào DW (chưa quyết định). Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: scripts/transform_era5_to_silver.py: K → °C, Pa → hPa, m → mm, gió từ u/v (tốc độ và hướng gió thổi đến), mây 0–1 → %, độ ẩm tính từ nhiệt độ và điểm sương (công thức Magnus); ô lưới gần nhất ghi ở grid_latitude/grid_longitude. Mưa ERA5 theo giờ đã là tổng từng giờ nên không cần khử cộng dồn (chỉ ERA5-Land cần). 701.376 dòng, 0 giá trị bị loại. So sánh với Open-Meteo (scripts/compare_era5_open_meteo.py): nhiệt độ tương quan 0,96–0,98; áp suất ở LCA, HBI lệch nhiều do độ cao ô lưới. Chưa nạp ERA5 vào DW (chưa quyết định). 23/10: đã chốt nạp ERA5 vào DW (701.376 dòng, task 18). Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2753,15 +2753,15 @@
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N20" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O20" s="24" t="inlineStr">
         <is>
-          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn 23/10: Gold mỗi tháng gồm cả ERA5 (3 nguồn: Open-Meteo, Meteostat, ERA5). Chưa có bảng pivot đa nguồn cho ML. 23/10: bảng Gold ML gộp nguồn (scripts/build_ml_pivot.py, gold/ml_pivot/weather_hourly_by_source_v1): mỗi dòng là một điểm × một giờ UTC, mỗi nguồn có cột riêng cho 8 biến (24 cột), không cộng gộp giữa các nguồn, thiếu thì để trống. 2016–2025: 701.376 dòng; số dòng, số giá trị và tổng từng cột khớp Gold, số dòng từng nguồn × năm khớp DW. Có manifest ghi nguồn gốc (SHA-256 các file Gold). Mô hình CART v1 không dùng bảng này; DW không đổi. Chờ bạn xác nhận Hoàn thành</t>
+          <t>21/10: Gold 2016–2025 nạp lại trên máy N1/N2, 120 tháng, 0 lỗi: 832.436 dòng (233 s) trước khi lọc Meteostat, sau đó 788.861 dòng (292 s). 22/10: nạp lại toàn bộ 2016–2025 (176 s, 0 lỗi, DW không đổi): cả 120 file Gold lưu station_key dạng số nguyên. Bộ đặc trưng ML nằm ở gold/ml_features (ID 23); chưa có bảng pivot đa nguồn 23/10: Gold mỗi tháng gồm cả ERA5 (3 nguồn: Open-Meteo, Meteostat, ERA5). Chưa có bảng pivot đa nguồn cho ML. 23/10: bảng Gold ML gộp nguồn (scripts/build_ml_pivot.py, gold/ml_pivot/weather_hourly_by_source_v1): mỗi dòng là một điểm × một giờ UTC, mỗi nguồn có cột riêng cho 8 biến (24 cột), không cộng gộp giữa các nguồn, thiếu thì để trống. 2016–2025: 701.376 dòng; số dòng, số giá trị và tổng từng cột khớp Gold, số dòng từng nguồn × năm khớp DW. Có manifest ghi nguồn gốc (SHA-256 các file Gold). Mô hình CART v1 không dùng bảng này; DW không đổi. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2807,15 +2807,15 @@
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N21" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): Open-Meteo, Meteostat, mưa ngày GHCNh: tải → Silver → seed dim → Gold/DW → đối chiếu DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy: 2024 HAN, chạy lại không thêm dòng, cố ý tắt MinIO rồi chạy tiếp thành công, 2024 cả 8 điểm, và cả 2016–2025 (3 phút 43 giây; khớp 788.861 dòng giờ và 17.866 ngày mưa; không tải lại gì). Cửa sổ nhỏ nhất 1 năm × 1 điểm (đã chốt). Chờ bạn xác nhận Hoàn thành 23/10: thêm nhánh ERA5 (tải time-series → Silver) trước bước quality_gate. Chạy 2016–2025: 14/14 task thành công (lần đầu bước ERA5 lỗi vì container Airflow chưa có khóa CDS; đã sửa, chạy tiếp từ bước lỗi); đối chiếu 1.490.237 = 1.490.237 dòng giờ, 17.866 = 17.866 ngày mưa.</t>
+          <t>22/10: dags/dag_weather_pipeline.py (weather_bronze_to_dw_dag): Open-Meteo, Meteostat, mưa ngày GHCNh: tải → Silver → seed dim → Gold/DW → đối chiếu DW với Silver (scripts/reconcile_dw.py). Tham số năm 2016–2025 và điểm; chạy tay, 1 lượt một lúc. Đã chạy: 2024 HAN, chạy lại không thêm dòng, cố ý tắt MinIO rồi chạy tiếp thành công, 2024 cả 8 điểm, và cả 2016–2025 (3 phút 43 giây; khớp 788.861 dòng giờ và 17.866 ngày mưa; không tải lại gì). Cửa sổ nhỏ nhất 1 năm × 1 điểm (đã chốt). 23/10: thêm nhánh ERA5 (tải time-series → Silver) trước bước quality_gate. Chạy 2016–2025: 14/14 task thành công (lần đầu bước ERA5 lỗi vì container Airflow chưa có khóa CDS; đã sửa, chạy tiếp từ bước lỗi); đối chiếu 1.490.237 = 1.490.237 dòng giờ, 17.866 = 17.866 ngày mưa. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2859,15 +2859,15 @@
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N22" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O22" s="24" t="inlineStr">
         <is>
-          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; lần nạp cuối 292 s (bản trước ghi 3.493 s là sai). 22/10: phạm vi xóa khi nạp lại tính theo phạm vi yêu cầu (nguồn biến mất bị xóa; thiếu file Silver Open-Meteo của một vị trí thì tháng đó báo lỗi); thêm pressure_type (sql/05). Chạy lại 2024 trên trạng thái hiện tại: 79.039 dòng, không đổi. Bản 994.145 dòng trên máy bacnx đã lỗi thời 23/10: nạp thêm ERA5 701.376 dòng (đã chốt nạp ERA5 theo đề cương §8, §10); DW 1.490.237 dòng, 0 trùng khóa; Open-Meteo, Meteostat, mưa ngày, dự báo không đổi.</t>
+          <t>21/10: DW sạch: 788.861 dòng (Open-Meteo 701.376 + Meteostat HAN 87.485), 0 trùng khóa; rút dòng sai đã kiểm chứng trên dữ liệu thật; lần nạp cuối 292 s (bản trước ghi 3.493 s là sai). 22/10: phạm vi xóa khi nạp lại tính theo phạm vi yêu cầu (nguồn biến mất bị xóa; thiếu file Silver Open-Meteo của một vị trí thì tháng đó báo lỗi); thêm pressure_type (sql/05). Chạy lại 2024 trên trạng thái hiện tại: 79.039 dòng, không đổi. Bản 994.145 dòng trên máy bacnx đã lỗi thời 23/10: nạp thêm ERA5 701.376 dòng (đã chốt nạp ERA5 theo đề cương §8, §10); DW 1.490.237 dòng, 0 trùng khóa; Open-Meteo, Meteostat, mưa ngày, dự báo không đổi. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -2911,15 +2911,15 @@
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N23" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O23" s="24" t="inlineStr">
         <is>
-          <t>21/10: sql/02_olap_views.sql (6 view giờ/ngày/tháng/năm/độ phủ), ngày mưa ≥1 mm, ngày nóng ≥35 °C; đối soát giờ→ngày→tháng→năm khớp 0 chênh trên 788.861 dòng; 3 test tích hợp. Chưa dùng trong Power BI</t>
+          <t>21/10: sql/02_olap_views.sql (6 view giờ/ngày/tháng/năm/độ phủ), ngày mưa ≥1 mm, ngày nóng ≥35 °C; đối soát giờ→ngày→tháng→năm khớp 0 chênh trên 788.861 dòng; 3 test tích hợp. Chưa dùng trong Power BI. 23/10: view có trong gói Power BI đã gửi (DW 1.490.237 dòng); dựng lại đúng trên môi trường sạch (task 34). Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3171,15 +3171,15 @@
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N28" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O28" s="24" t="inlineStr">
         <is>
-          <t>22/10: scripts/quality_gate.py, task quality_gate trong DAG (sau bước Silver, trước khi ghi DW). Dừng DAG khi: thiếu cột hoặc khóa trống; giờ không UTC hoặc sai tháng; trùng nguồn × điểm × giờ; giá trị ngoài khoảng hợp lệ của data-contract; thiếu giờ Open-Meteo; GHCNh trùng ngày, sai khung 12:00 UTC, mưa ngoài 0–999 mm. Cảnh báo, không dừng (ngưỡng chốt 22/10 từ dữ liệu 2016–2025): độ phủ Meteostat &lt; 95%, GHCNh &lt; 90%; Open-Meteo thiếu giá trị; Meteostat thiếu nhiệt độ/độ ẩm &gt; 5%; nhiệt độ ngoài 0–45 °C; áp suất ngoài 950–1050 hPa; mưa giờ &gt; 100 mm; mưa ngày ≥ 300 mm chưa duyệt. Dữ liệu thật 2016–2025: 712 kiểm tra, 0 lỗi, 0 cảnh báo; DAG 2024 HAN 12/12 task; test tích hợp xác nhận task Airflow báo lỗi khi Silver sai. Chờ bạn xác nhận Hoàn thành 23/10: kiểm tra cả ERA5 (bắt buộc đủ giờ; cảnh báo áp suất ngoài 900–1050 hPa vì ô lưới cao hơn điểm): 1.032 kiểm tra, 0 lỗi, 0 cảnh báo.</t>
+          <t>22/10: scripts/quality_gate.py, task quality_gate trong DAG (sau bước Silver, trước khi ghi DW). Dừng DAG khi: thiếu cột hoặc khóa trống; giờ không UTC hoặc sai tháng; trùng nguồn × điểm × giờ; giá trị ngoài khoảng hợp lệ của data-contract; thiếu giờ Open-Meteo; GHCNh trùng ngày, sai khung 12:00 UTC, mưa ngoài 0–999 mm. Cảnh báo, không dừng (ngưỡng chốt 22/10 từ dữ liệu 2016–2025): độ phủ Meteostat &lt; 95%, GHCNh &lt; 90%; Open-Meteo thiếu giá trị; Meteostat thiếu nhiệt độ/độ ẩm &gt; 5%; nhiệt độ ngoài 0–45 °C; áp suất ngoài 950–1050 hPa; mưa giờ &gt; 100 mm; mưa ngày ≥ 300 mm chưa duyệt. Dữ liệu thật 2016–2025: 712 kiểm tra, 0 lỗi, 0 cảnh báo; DAG 2024 HAN 12/12 task; test tích hợp xác nhận task Airflow báo lỗi khi Silver sai. 23/10: kiểm tra cả ERA5 (bắt buộc đủ giờ; cảnh báo áp suất ngoài 900–1050 hPa vì ô lưới cao hơn điểm): 1.032 kiểm tra, 0 lỗi, 0 cảnh báo. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3223,15 +3223,15 @@
       </c>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N29" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O29" s="24" t="inlineStr">
         <is>
-          <t>23/10: DAG weather_incremental_dag chạy theo lịch hằng ngày (không chạy bù quá khứ, tạm dừng khi mới tạo): đọc mốc watermark trong MinIO (năm cuối đã nạp và đối chiếu xong) → chọn năm mới tiếp theo + chạy lại 1 năm trước để lấy dữ liệu sửa muộn, không vượt quá 2025 → gọi DAG Bronze→DW (task 17) và chờ → chỉ dời mốc khi lần chạy đó thành công. Chạy thật: đặt mốc 2024, lần chạy theo lịch xử lý 2024–2025 (14/14 task, 3 phút, đối chiếu 298.192 = 298.192 dòng giờ), mốc dời lên 2025; DW giống hệt trước khi chạy (không trùng, không đổi giá trị); lần chạy sau tự bỏ qua vì đã đủ đến 2025. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: DAG weather_incremental_dag chạy theo lịch hằng ngày (không chạy bù quá khứ, tạm dừng khi mới tạo): đọc mốc watermark trong MinIO (năm cuối đã nạp và đối chiếu xong) → chọn năm mới tiếp theo + chạy lại 1 năm trước để lấy dữ liệu sửa muộn, không vượt quá 2025 → gọi DAG Bronze→DW (task 17) và chờ → chỉ dời mốc khi lần chạy đó thành công. Chạy thật: đặt mốc 2024, lần chạy theo lịch xử lý 2024–2025 (14/14 task, 3 phút, đối chiếu 298.192 = 298.192 dòng giờ), mốc dời lên 2025; DW giống hệt trước khi chạy (không trùng, không đổi giá trị); lần chạy sau tự bỏ qua vì đã đủ đến 2025. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3277,15 +3277,15 @@
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N30" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O30" s="24" t="inlineStr">
         <is>
-          <t>23/10: đo thật bằng scripts/benchmark_dw_queries.py (EXPLAIN ANALYZE, 3 lần, trung vị) trên DW 1.490.237 dòng: nạp từng view cho dashboard 0,3–1,3 giây, tổng khoảng 5,8 giây; truy vấn đối chiếu 0,4 ms–1,2 giây. Index hiện có đã đủ cho truy vấn có lọc; đã thử thêm index ghép và index cho 4 khóa ngoại trong giao dịch rồi hoàn tác: không nhanh hơn (view tổng hợp phải quét cả bảng), nên không thêm. Mục tiêu đã chốt 23/10: mỗi view dưới 5 giây, truy vấn đối chiếu dưới 2 giây (đang đạt: tối đa 1,3 giây và 1,2 giây). Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: đo thật bằng scripts/benchmark_dw_queries.py (EXPLAIN ANALYZE, 3 lần, trung vị) trên DW 1.490.237 dòng: nạp từng view cho dashboard 0,3–1,3 giây, tổng khoảng 5,8 giây; truy vấn đối chiếu 0,4 ms–1,2 giây. Index hiện có đã đủ cho truy vấn có lọc; đã thử thêm index ghép và index cho 4 khóa ngoại trong giao dịch rồi hoàn tác: không nhanh hơn (view tổng hợp phải quét cả bảng), nên không thêm. Mục tiêu đã chốt 23/10: mỗi view dưới 5 giây, truy vấn đối chiếu dưới 2 giây (đang đạt: tối đa 1,3 giây và 1,2 giây). Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3533,15 +3533,15 @@
       </c>
       <c r="M35" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N35" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu đã phát hiện lỗi nhãn ID 22 (đã sửa); ma trận nhầm lẫn DW = kết quả chấm lại. sql/05: dim_model ghi rõ nhãn của từng chỉ số (chọn trên v0.2, F1 val 0,786; test trên v0.2.1, F1 val trên nhãn này 0,789). Do N1/N2 làm thay N3</t>
+          <t>22/10: sql/04_predictions.sql (dim_model, khóa duy nhất model × vị trí × origin UTC, cửa sổ mục tiêu, view vw_prediction_vs_actual) + scripts/load_predictions.py. Đã nạp 69.888 dự đoán test 2025, chạy lại không trùng. View đối chiếu đã phát hiện lỗi nhãn ID 22 (đã sửa); ma trận nhầm lẫn DW = kết quả chấm lại. sql/05: dim_model ghi rõ nhãn của từng chỉ số (chọn trên v0.2, F1 val 0,786; test trên v0.2.1, F1 val trên nhãn này 0,789). Do N1/N2 làm thay N3. 23/10: dựng lại đúng trên môi trường sạch (task 34). Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3587,15 +3587,15 @@
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N36" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O36" s="24" t="inlineStr">
         <is>
-          <t>23/10: DAG weather_rain_scoring_dag (chạy tay): kiểm tra khoảng ngày → chấm điểm (scripts/score_cart.py: kiểm tra SHA-256 của mô hình, tính lại đặc trưng từ Silver, thiếu dữ liệu thì báo lỗi) → ghi Gold mỗi ngày một file → đăng lên DW (scripts/publish_predictions.py: chỉ ghi dòng thay đổi) → đối chiếu DW với Gold. Chỉ đăng dự báo tập test 2025 (01/01–30/12, mục tiêu không sang 2026). Chạy thật cả năm 2025: 4/4 task thành công trong 40 giây, 69.888 dự báo, DW không đổi dòng nào (mã băm trước và sau giống hệt); thử khoảng ngày sai thì DAG dừng ngay ở bước đầu. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: DAG weather_rain_scoring_dag (chạy tay): kiểm tra khoảng ngày → chấm điểm (scripts/score_cart.py: kiểm tra SHA-256 của mô hình, tính lại đặc trưng từ Silver, thiếu dữ liệu thì báo lỗi) → ghi Gold mỗi ngày một file → đăng lên DW (scripts/publish_predictions.py: chỉ ghi dòng thay đổi) → đối chiếu DW với Gold. Chỉ đăng dự báo tập test 2025 (01/01–30/12, mục tiêu không sang 2026). Chạy thật cả năm 2025: 4/4 task thành công trong 40 giây, 69.888 dự báo, DW không đổi dòng nào (mã băm trước và sau giống hệt); thử khoảng ngày sai thì DAG dừng ngay ở bước đầu. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3687,15 +3687,15 @@
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N38" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O38" s="24" t="inlineStr">
         <is>
-          <t>23/10: chạy lại toàn bộ trên môi trường sạch (clone repo mới, volume Docker trống, tải lại mọi nguồn): DAG Bronze→DW 14/14 bước ngay lần đầu, 15 phút; kiểm tra chất lượng 1.032 lượt 0 lỗi; đối chiếu 1.490.237 dòng giờ, 17.866 ngày mưa. So với máy hiện tại: mọi bảng DW khớp theo khóa tự nhiên; Silver/Gold khớp từng byte; chỉ khác dấu thời gian tải và ID tự tăng. Huấn luyện lại ra đúng mô hình v1 (cùng SHA-256). Chạy lại và chạy lỗi đều đúng. Tìm ra và đã sửa 1 lỗi: trên máy mới, lệnh huấn luyện mặc định có thể lưu mô hình khác dưới tên v1; giờ v1 được ghim SHA-256 và có gói phát hành (scripts/model_release.py). Hướng dẫn: docs/reproduce-from-scratch.md. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: chạy lại toàn bộ trên môi trường sạch (clone repo mới, volume Docker trống, tải lại mọi nguồn): DAG Bronze→DW 14/14 bước ngay lần đầu, 15 phút; kiểm tra chất lượng 1.032 lượt 0 lỗi; đối chiếu 1.490.237 dòng giờ, 17.866 ngày mưa. So với máy hiện tại: mọi bảng DW khớp theo khóa tự nhiên; Silver/Gold khớp từng byte; chỉ khác dấu thời gian tải và ID tự tăng. Huấn luyện lại ra đúng mô hình v1 (cùng SHA-256). Chạy lại và chạy lỗi đều đúng. Tìm ra và đã sửa 1 lỗi: trên máy mới, lệnh huấn luyện mặc định có thể lưu mô hình khác dưới tên v1; giờ v1 được ghim SHA-256 và có gói phát hành (scripts/model_release.py). Hướng dẫn: docs/reproduce-from-scratch.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>

--- a/Phan_cong_cong_viec_DW_khi_tuong.xlsx
+++ b/Phan_cong_cong_viec_DW_khi_tuong.xlsx
@@ -2291,7 +2291,7 @@
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>Hoàn thành 21/10: rain-label.md v0.2: ngưỡng 1 mm, nguồn Open-Meteo, cửa sổ (t,t+24h] đã kiểm chứng, thiếu giờ thì bỏ nhãn. Tỷ lệ Yes 50,5% đo bằng bản v0.2; bản v0.2.1 (sửa lỗi cộng số thực 22/10): train 51,6% / val 50,1% / test 49,7%. Nhóm xác nhận qua N1/N2; N3 chưa duyệt. Còn mở có ghi rõ: fallback ERA5/trạm, ngưỡng độ phủ tối thiểu</t>
+          <t>Hoàn thành 21/10: rain-label.md v0.2: ngưỡng 1 mm, nguồn Open-Meteo, cửa sổ (t,t+24h] đã kiểm chứng, thiếu giờ thì bỏ nhãn. Tỷ lệ Yes 50,5% đo bằng bản v0.2; bản v0.2.1 (sửa lỗi cộng số thực 22/10): train 51,6% / val 50,1% / test 49,7%. Nhóm xác nhận qua N1/N2; N3 chưa duyệt. Còn mở có ghi rõ: fallback ERA5/trạm, ngưỡng độ phủ tối thiểu. 23/10: N3 đã duyệt.</t>
         </is>
       </c>
     </row>
@@ -2387,15 +2387,15 @@
       </c>
       <c r="M13" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N13" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O13" s="24" t="inlineStr">
         <is>
-          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. 22/10: trạm Meteostat 48820 thực chất là sân bay Nội Bài (cách điểm HAN 22 km), đã ghi lại; quy tắc cực trị so sánh theo độ phân giải 0,1 mm. Bronze Meteostat lưu CSV đã giải nén, chưa có manifest/SHA. Chờ nhóm duyệt quy tắc cực trị 300 mm 23/10: Bronze Meteostat lưu nguyên file .csv.gz nhận về kèm manifest (SHA-256, URL, thời điểm tải); 15 file CSV cũ được thay sau khi kiểm tra bản tải mới giải nén giống hệt từng byte; 25 năm-trạm không có dữ liệu (HTTP 404) được ghi lại nên lần sau không hỏi lại. Silver Meteostat kiểm tra SHA-256, chạy lại giống hệt (120 file, 87.485 dòng); DW không đổi. Chạy chuỗi DAG 2024 × HAN trong container không có Internet: 13/13 bước thành công.</t>
+          <t>21/10: Meteostat chỉ giữ quan trắc thật (HAN). NOAA GHCNh mưa 24h cho 5 điểm (HPH, TNG, LCA, HAN≈Hà Đông, NBI≈Nam Định) 2016–2025: 17.866 ngày, độ phủ 95,9–99,2%, bảng fact_station_daily_rain + view so sánh với Open-Meteo. 22/10: trạm Meteostat 48820 thực chất là sân bay Nội Bài (cách điểm HAN 22 km), đã ghi lại; quy tắc cực trị so sánh theo độ phân giải 0,1 mm. Bronze Meteostat lưu CSV đã giải nén, chưa có manifest/SHA. Quy tắc cực trị 300 mm chờ nhóm duyệt. 23/10: Bronze Meteostat lưu nguyên file .csv.gz nhận về kèm manifest (SHA-256, URL, thời điểm tải); 15 file CSV cũ được thay sau khi kiểm tra bản tải mới giải nén giống hệt từng byte; 25 năm-trạm không có dữ liệu (HTTP 404) được ghi lại nên lần sau không hỏi lại. Silver Meteostat kiểm tra SHA-256, chạy lại giống hệt (120 file, 87.485 dòng); DW không đổi. Chạy chuỗi DAG 2024 × HAN trong container không có Internet: 13/13 bước thành công. 23/10: đã duyệt quy tắc cực trị 300 mm (2016–2025 chỉ cách ly 1 ngày: Nam Định 13/10/2023, 700 mm; giữ 2 trận có thật 491,3 mm và 338 mm). Ngưỡng 300 mm và 10% là ngưỡng nhóm tự đặt. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3015,15 +3015,15 @@
       </c>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N25" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>22/10: notebooks/eda_rain_next24h.ipynb (nhãn đã sửa), chỉ dùng train để chọn biến: mùa vụ mạnh theo tháng giờ Việt Nam (T8 78,6%, T12 26,5%; bản trước dùng tháng UTC), giờ trong ngày gần như không ảnh hưởng (51,3-52,0%), biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm. Thêm bảng tương quan Spearman: cặp mạnh độ ẩm–chênh điểm sương (-1,00), nhiệt độ–điểm sương (0,87), điểm sương–áp suất (-0,80). Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3</t>
+          <t>22/10: notebooks/eda_rain_next24h.ipynb (nhãn đã sửa), chỉ dùng train để chọn biến: mùa vụ mạnh theo tháng giờ Việt Nam (T8 78,6%, T12 26,5%; bản trước dùng tháng UTC), giờ trong ngày gần như không ảnh hưởng (51,3-52,0%), biến tách tốt nhất: điểm sương, mưa 24h trước, độ ẩm. Thêm bảng tương quan Spearman: cặp mạnh độ ẩm–chênh điểm sương (-1,00), nhiệt độ–điểm sương (0,87), điểm sương–áp suất (-0,80). Logic trong scripts/rain_eda.py có test. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3067,15 +3067,15 @@
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N26" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O26" s="24" t="inlineStr">
         <is>
-          <t>22/10: nhãn v2 (rain_next24h_v0.2.1) gold/ml_labels/rain_next24h_labels_v2.parquet: 700.800 nhãn dùng được, Yes 51,6% / 50,1% / 49,7% (train/val/test), 576 loại ở ranh giới. Đã sửa lỗi cộng số thực: bản v1 gán Không mưa cho 5.147 cửa sổ đúng 1,0 mm (0,73%); phát hiện nhờ đối chiếu DW ở ID 31. Có test hồi quy. Do N1/N2 làm thay N3</t>
+          <t>22/10: nhãn v2 (rain_next24h_v0.2.1) gold/ml_labels/rain_next24h_labels_v2.parquet: 700.800 nhãn dùng được, Yes 51,6% / 50,1% / 49,7% (train/val/test), 576 loại ở ranh giới. Đã sửa lỗi cộng số thực: bản v1 gán Không mưa cho 5.147 cửa sổ đúng 1,0 mm (0,73%); phát hiện nhờ đối chiếu DW ở ID 31. Có test hồi quy. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3119,15 +3119,15 @@
       </c>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N27" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O27" s="24" t="inlineStr">
         <is>
-          <t>22/10: đặc trưng v2 gold/ml_features/cart_rain_{train_2016_2023,val_2024,test_2025}_v2.parquet + manifest (nhãn v0.2.1, tổng mưa làm tròn); v1 giữ cho model v1. 22 đặc trưng chỉ từ Open-Meteo, 700.800 dòng; thiếu chỉ ở 24 giờ đầu 2016. Test chống rò rỉ, thiếu giờ, không lẫn vị trí. Do N1/N2 làm thay N3</t>
+          <t>22/10: đặc trưng v2 gold/ml_features/cart_rain_{train_2016_2023,val_2024,test_2025}_v2.parquet + manifest (nhãn v0.2.1, tổng mưa làm tròn); v1 giữ cho model v1. 22 đặc trưng chỉ từ Open-Meteo, 700.800 dòng; thiếu chỉ ở 24 giờ đầu 2016. Test chống rò rỉ, thiếu giờ, không lẫn vị trí. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3375,15 +3375,15 @@
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N32" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O32" s="24" t="inlineStr">
         <is>
-          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. 22/10: chặn ghi đè model (model đã chấm test thì không cho ghi đè). Chọn cấu hình và ngưỡng theo F1. Quy tắc ưu tiên Recall đã chốt 22/10: ngưỡng 0,36 (Recall validation 0,88); 0,40 vẫn là kết quả test chính thức. Chờ N3 duyệt (rain-label.md). Do N1/N2 làm thay N3</t>
+          <t>21/10: gold/ml_models/cart_rain_next24h_v1 (model.joblib + report.json). Lưới 120 cấu hình, chọn trên validation 2024: max_depth=8, min_samples_leaf=50, class_weight=balanced, ccp_alpha=1e-4, 88 lá, ngưỡng 0,40. Validation (nhãn đã sửa 22/10): Precision 0,760 / Recall 0,819 / F1 0,789. Model train trên nhãn v1 (0,73% sai), không train lại để giữ test độc lập. 22/10: chặn ghi đè model (model đã chấm test thì không cho ghi đè). Chọn cấu hình và ngưỡng theo F1. Quy tắc ưu tiên Recall đã chốt 22/10: ngưỡng 0,36 (Recall validation 0,88); 0,40 vẫn là kết quả test chính thức. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3427,15 +3427,15 @@
       </c>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N33" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>22/10: đánh giá 1 lần trên test 2025, model + ngưỡng 0,40 chốt từ validation. Chấm lại với nhãn đã sửa (dự đoán giữ nguyên, kiểm SHA-256 model): TP 27.467 / FP 8.569 / TN 26.617 / FN 7.235; Accuracy 0,774, Precision 0,762, Recall 0,792, F1 0,777 (dự báo theo hiện trạng F1 0,729). Mùa mưa F1 0,836, mùa khô 0,624. Khớp hoàn toàn với view DW. test_predictions.parquet giữ nhãn cũ v0.2: phân tích lấy nhãn từ đặc trưng v2. Do N1/N2 làm thay N3</t>
+          <t>22/10: đánh giá 1 lần trên test 2025, model + ngưỡng 0,40 chốt từ validation. Chấm lại với nhãn đã sửa (dự đoán giữ nguyên, kiểm SHA-256 model): TP 27.467 / FP 8.569 / TN 26.617 / FN 7.235; Accuracy 0,774, Precision 0,762, Recall 0,792, F1 0,777 (dự báo theo hiện trạng F1 0,729). Mùa mưa F1 0,836, mùa khô 0,624. Khớp hoàn toàn với view DW. test_predictions.parquet giữ nhãn cũ v0.2: phân tích lấy nhãn từ đặc trưng v2. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3479,15 +3479,15 @@
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N34" s="23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O34" s="24" t="inlineStr">
         <is>
-          <t>22/10: notebooks/cart_tree_rules.ipynb (SHA-256 đúng model ID 29): hình 3 tầng đầu, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025, hồ sơ ca bỏ sót trên validation (nhãn đã sửa): 65% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,5%). Đã sửa lời diễn giải «mưa không báo trước». Ý tưởng thêm hướng gió đến từ một ví dụ test 2025: phải chứng minh bằng EDA trên train trước. Do N1/N2 làm thay N3</t>
+          <t>22/10: notebooks/cart_tree_rules.ipynb (SHA-256 đúng model ID 29): hình 3 tầng đầu, 88 luật bằng tên + đơn vị thật, độ quan trọng, 4 ví dụ test 2025, hồ sơ ca bỏ sót trên validation (nhãn đã sửa): 65% dưới 5 mm, 55% xác suất 0,30-0,40, mưa sau 24h khô chỉ bắt được 17% (mùa khô 2,5%). Đã sửa lời diễn giải «mưa không báo trước». Ý tưởng thêm hướng gió đến từ một ví dụ test 2025: phải chứng minh bằng EDA trên train trước. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
@@ -3785,15 +3785,15 @@
       </c>
       <c r="M40" s="22" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N40" s="23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O40" s="24" t="inlineStr">
         <is>
-          <t>23/10: scripts/analyze_cart_thresholds.py → gold/ml_models/cart_rain_next24h_v1/threshold_error_analysis.json. So sánh ngưỡng trên validation 2024 (lưới 0,30–0,70 của quy tắc chọn ngưỡng): quy tắc F1 vẫn ra 0,40 (ngưỡng chính thức), quy tắc ưu tiên Recall ra 0,36. Test 2025 chỉ tính ở các ngưỡng đã chốt (phân tích sau, có ghi rõ): 0,40 → P 0,762 / R 0,792 / F1 0,777; 0,36 → 0,723 / 0,848 / 0,780 (thêm 2.709 báo động giả, bớt 1.945 ca bỏ sót). Lỗi: bỏ sót nhiều nhất ở mưa nhẹ 1–2 mm (42%); báo động giả phần lớn là cửa sổ có 0–1 mm; mưa sau 24 giờ khô chỉ bắt được 17%; mùa mưa F1 0,836, mùa khô 0,624. Chi tiết: rain-label.md. Do N1/N2 làm thay N3. Chờ bạn xác nhận Hoàn thành</t>
+          <t>23/10: scripts/analyze_cart_thresholds.py → gold/ml_models/cart_rain_next24h_v1/threshold_error_analysis.json. So sánh ngưỡng trên validation 2024 (lưới 0,30–0,70 của quy tắc chọn ngưỡng): quy tắc F1 vẫn ra 0,40 (ngưỡng chính thức), quy tắc ưu tiên Recall ra 0,36. Test 2025 chỉ tính ở các ngưỡng đã chốt (phân tích sau, có ghi rõ): 0,40 → P 0,762 / R 0,792 / F1 0,777; 0,36 → 0,723 / 0,848 / 0,780 (thêm 2.709 báo động giả, bớt 1.945 ca bỏ sót). Lỗi: bỏ sót nhiều nhất ở mưa nhẹ 1–2 mm (42%); báo động giả phần lớn là cửa sổ có 0–1 mm; mưa sau 24 giờ khô chỉ bắt được 17%; mùa mưa F1 0,836, mùa khô 0,624. Chi tiết: rain-label.md. Do N1/N2 làm thay N3. 23/10: N3 đã duyệt 8 mục quyết định ML trong rain-label.md. Xác nhận Hoàn thành 23/10.</t>
         </is>
       </c>
     </row>
